--- a/NEW BOT 02/Fan_Assemble_Inventory_Movement.xlsx
+++ b/NEW BOT 02/Fan_Assemble_Inventory_Movement.xlsx
@@ -624,28 +624,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Production Module ⟶ Advance Production Reports ⟶ Inventory Movement Report(221023) ⟶ Inventory Name: Fan Assemble  |  Company: FAN  |  Date Range: 2026-09-01 to 2026-09-19</t>
+          <t>Production Module ⟶ Advance Production Reports ⟶ Inventory Movement Report(221023) ⟶ Inventory Name: Fan Assemble  |  Company: FAN  |  Date Range: 2026-09-01 to 2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>2,542,768.42</t>
+          <t>2,590,938.42</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>1,211,898.53</t>
+          <t>1,199,200.58</t>
         </is>
       </c>
       <c r="I5" s="4" t="n"/>
@@ -728,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T190"/>
+  <dimension ref="A1:T191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1115,19 +1115,19 @@
         <v>0</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="M7" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="P7" s="19" t="n">
         <v>0</v>
@@ -1186,19 +1186,19 @@
         <v>0</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>8580</v>
+        <v>9380</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>8580</v>
+        <v>9380</v>
       </c>
       <c r="M8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>8580</v>
+        <v>9380</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>8580</v>
+        <v>9380</v>
       </c>
       <c r="P8" s="16" t="n">
         <v>0</v>
@@ -1541,19 +1541,19 @@
         <v>0</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="M13" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="P13" s="19" t="n">
         <v>0</v>
@@ -1760,19 +1760,19 @@
         <v>35426</v>
       </c>
       <c r="M16" s="16" t="n">
-        <v>26852</v>
+        <v>26901</v>
       </c>
       <c r="N16" s="16" t="n">
         <v>87</v>
       </c>
       <c r="O16" s="16" t="n">
-        <v>26939</v>
+        <v>26988</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>8487</v>
+        <v>8438</v>
       </c>
       <c r="Q16" s="16" t="n">
-        <v>8487</v>
+        <v>8438</v>
       </c>
       <c r="R16" s="16" t="n">
         <v>0</v>
@@ -1831,19 +1831,19 @@
         <v>35307</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>26852</v>
+        <v>26901</v>
       </c>
       <c r="N17" s="19" t="n">
         <v>87</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>26939</v>
+        <v>26988</v>
       </c>
       <c r="P17" s="19" t="n">
-        <v>8368</v>
+        <v>8319</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>8368</v>
+        <v>8319</v>
       </c>
       <c r="R17" s="19" t="n">
         <v>0</v>
@@ -1973,19 +1973,19 @@
         <v>1733.3765</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>898.2809999999999</v>
+        <v>899.457</v>
       </c>
       <c r="N19" s="19" t="n">
         <v>2.104</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>900.385</v>
+        <v>901.561</v>
       </c>
       <c r="P19" s="19" t="n">
-        <v>832.9915</v>
+        <v>831.8155</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>832.9915</v>
+        <v>831.8155</v>
       </c>
       <c r="R19" s="19" t="n">
         <v>-0</v>
@@ -2115,19 +2115,19 @@
         <v>292.18</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>44.416</v>
+        <v>45.2</v>
       </c>
       <c r="N21" s="19" t="n">
         <v>1.36</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>45.776</v>
+        <v>46.56</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>246.404</v>
+        <v>245.62</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>246.404</v>
+        <v>245.62</v>
       </c>
       <c r="R21" s="19" t="n">
         <v>0</v>
@@ -2399,19 +2399,19 @@
         <v>47462</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>45624</v>
+        <v>47424</v>
       </c>
       <c r="N25" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>45624</v>
+        <v>47424</v>
       </c>
       <c r="P25" s="19" t="n">
-        <v>1838</v>
+        <v>38</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>1838</v>
+        <v>38</v>
       </c>
       <c r="R25" s="19" t="n">
         <v>0</v>
@@ -2470,19 +2470,19 @@
         <v>182435</v>
       </c>
       <c r="M26" s="16" t="n">
-        <v>45624</v>
+        <v>47424</v>
       </c>
       <c r="N26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>45624</v>
+        <v>47424</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>136811</v>
+        <v>135011</v>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>136811</v>
+        <v>135011</v>
       </c>
       <c r="R26" s="16" t="n">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         <v>10181</v>
       </c>
       <c r="M30" s="16" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="N30" s="16" t="n">
         <v>60</v>
       </c>
       <c r="O30" s="16" t="n">
-        <v>7475</v>
+        <v>7524</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>2706</v>
+        <v>2657</v>
       </c>
       <c r="Q30" s="16" t="n">
-        <v>2706</v>
+        <v>2657</v>
       </c>
       <c r="R30" s="16" t="n">
         <v>0</v>
@@ -2896,19 +2896,19 @@
         <v>48710</v>
       </c>
       <c r="M32" s="16" t="n">
-        <v>26852</v>
+        <v>26901</v>
       </c>
       <c r="N32" s="16" t="n">
         <v>85</v>
       </c>
       <c r="O32" s="16" t="n">
-        <v>26937</v>
+        <v>26986</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>21773</v>
+        <v>21724</v>
       </c>
       <c r="Q32" s="16" t="n">
-        <v>21773</v>
+        <v>21724</v>
       </c>
       <c r="R32" s="16" t="n">
         <v>0</v>
@@ -3180,19 +3180,19 @@
         <v>18.8715</v>
       </c>
       <c r="M36" s="16" t="n">
-        <v>10.781</v>
+        <v>10.8055</v>
       </c>
       <c r="N36" s="16" t="n">
         <v>0.0425</v>
       </c>
       <c r="O36" s="16" t="n">
-        <v>10.8235</v>
+        <v>10.848</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>8.048</v>
+        <v>8.0235</v>
       </c>
       <c r="Q36" s="16" t="n">
-        <v>8.048</v>
+        <v>8.0235</v>
       </c>
       <c r="R36" s="16" t="n">
         <v>0</v>
@@ -3251,19 +3251,19 @@
         <v>505.675</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>277.225</v>
+        <v>302.075</v>
       </c>
       <c r="N37" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>277.225</v>
+        <v>302.075</v>
       </c>
       <c r="P37" s="19" t="n">
-        <v>228.45</v>
+        <v>203.6</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>228.45</v>
+        <v>203.6</v>
       </c>
       <c r="R37" s="19" t="n">
         <v>0</v>
@@ -3393,19 +3393,19 @@
         <v>85436</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>47015</v>
+        <v>50645</v>
       </c>
       <c r="N39" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>47015</v>
+        <v>50645</v>
       </c>
       <c r="P39" s="19" t="n">
-        <v>38421</v>
+        <v>34791</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>38421</v>
+        <v>34791</v>
       </c>
       <c r="R39" s="19" t="n">
         <v>0</v>
@@ -3464,19 +3464,19 @@
         <v>18153</v>
       </c>
       <c r="M40" s="16" t="n">
-        <v>8430</v>
+        <v>9770</v>
       </c>
       <c r="N40" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="16" t="n">
-        <v>8430</v>
+        <v>9770</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>9723</v>
+        <v>8383</v>
       </c>
       <c r="Q40" s="16" t="n">
-        <v>9723</v>
+        <v>8383</v>
       </c>
       <c r="R40" s="16" t="n">
         <v>0</v>
@@ -3606,19 +3606,19 @@
         <v>286331</v>
       </c>
       <c r="M42" s="16" t="n">
-        <v>55445</v>
+        <v>60415</v>
       </c>
       <c r="N42" s="16" t="n">
         <v>2</v>
       </c>
       <c r="O42" s="16" t="n">
-        <v>55447</v>
+        <v>60417</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>230884</v>
+        <v>225914</v>
       </c>
       <c r="Q42" s="16" t="n">
-        <v>230884</v>
+        <v>225914</v>
       </c>
       <c r="R42" s="16" t="n">
         <v>0</v>
@@ -3677,22 +3677,22 @@
         <v>10632.64</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>4296.32</v>
+        <v>4304.16</v>
       </c>
       <c r="N43" s="19" t="n">
         <v>13.92</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>4310.24</v>
+        <v>4318.08</v>
       </c>
       <c r="P43" s="19" t="n">
-        <v>6322.4</v>
+        <v>6314.56</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>6322.4</v>
+        <v>6314.56</v>
       </c>
       <c r="R43" s="19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S43" s="18" t="inlineStr"/>
     </row>
@@ -3748,19 +3748,19 @@
         <v>20317.5515</v>
       </c>
       <c r="M44" s="16" t="n">
-        <v>16379.72</v>
+        <v>16409.61</v>
       </c>
       <c r="N44" s="16" t="n">
         <v>53.07</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>16432.79</v>
+        <v>16462.68</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>3884.7615</v>
+        <v>3854.8715</v>
       </c>
       <c r="Q44" s="16" t="n">
-        <v>3884.7615</v>
+        <v>3854.8715</v>
       </c>
       <c r="R44" s="16" t="n">
         <v>0</v>
@@ -3819,19 +3819,19 @@
         <v>23286.89</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>16379.72</v>
+        <v>16409.61</v>
       </c>
       <c r="N45" s="19" t="n">
         <v>53.07</v>
       </c>
       <c r="O45" s="19" t="n">
-        <v>16432.79</v>
+        <v>16462.68</v>
       </c>
       <c r="P45" s="19" t="n">
-        <v>6854.1</v>
+        <v>6824.21</v>
       </c>
       <c r="Q45" s="19" t="n">
-        <v>6854.1</v>
+        <v>6824.21</v>
       </c>
       <c r="R45" s="19" t="n">
         <v>-0</v>
@@ -3890,19 +3890,19 @@
         <v>3.2392</v>
       </c>
       <c r="M46" s="16" t="n">
-        <v>2.1562</v>
+        <v>2.1611</v>
       </c>
       <c r="N46" s="16" t="n">
         <v>0.008699999999999999</v>
       </c>
       <c r="O46" s="16" t="n">
-        <v>2.1649</v>
+        <v>2.1698</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>1.0743</v>
+        <v>1.0694</v>
       </c>
       <c r="Q46" s="16" t="n">
-        <v>1.0743</v>
+        <v>1.0694</v>
       </c>
       <c r="R46" s="16" t="n">
         <v>0</v>
@@ -3961,19 +3961,19 @@
         <v>92732</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>22490</v>
+        <v>24190</v>
       </c>
       <c r="N47" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="19" t="n">
-        <v>22490</v>
+        <v>24190</v>
       </c>
       <c r="P47" s="19" t="n">
-        <v>70242</v>
+        <v>68542</v>
       </c>
       <c r="Q47" s="19" t="n">
-        <v>70242</v>
+        <v>68542</v>
       </c>
       <c r="R47" s="19" t="n">
         <v>0</v>
@@ -4103,19 +4103,19 @@
         <v>106.473</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>6.279</v>
+        <v>7.221</v>
       </c>
       <c r="N49" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O49" s="19" t="n">
-        <v>6.279</v>
+        <v>7.221</v>
       </c>
       <c r="P49" s="19" t="n">
-        <v>100.194</v>
+        <v>99.252</v>
       </c>
       <c r="Q49" s="19" t="n">
-        <v>100.194</v>
+        <v>99.252</v>
       </c>
       <c r="R49" s="19" t="n">
         <v>0</v>
@@ -4174,22 +4174,22 @@
         <v>76.702</v>
       </c>
       <c r="M50" s="16" t="n">
-        <v>26.852</v>
+        <v>26.901</v>
       </c>
       <c r="N50" s="16" t="n">
         <v>22.085</v>
       </c>
       <c r="O50" s="16" t="n">
-        <v>48.937</v>
+        <v>48.986</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>27.765</v>
+        <v>27.716</v>
       </c>
       <c r="Q50" s="16" t="n">
-        <v>27.765</v>
+        <v>27.716</v>
       </c>
       <c r="R50" s="16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S50" s="15" t="inlineStr"/>
     </row>
@@ -4387,19 +4387,19 @@
         <v>27552</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>26852</v>
+        <v>26901</v>
       </c>
       <c r="N53" s="19" t="n">
         <v>85</v>
       </c>
       <c r="O53" s="19" t="n">
-        <v>26937</v>
+        <v>26986</v>
       </c>
       <c r="P53" s="19" t="n">
-        <v>615</v>
+        <v>566</v>
       </c>
       <c r="Q53" s="19" t="n">
-        <v>615</v>
+        <v>566</v>
       </c>
       <c r="R53" s="19" t="n">
         <v>0</v>
@@ -4600,19 +4600,19 @@
         <v>75.5472</v>
       </c>
       <c r="M56" s="16" t="n">
-        <v>24.0107</v>
+        <v>26.7979</v>
       </c>
       <c r="N56" s="16" t="n">
         <v>0.0178</v>
       </c>
       <c r="O56" s="16" t="n">
-        <v>24.0285</v>
+        <v>26.8157</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>51.5187</v>
+        <v>48.7315</v>
       </c>
       <c r="Q56" s="16" t="n">
-        <v>29.2023</v>
+        <v>26.4151</v>
       </c>
       <c r="R56" s="16" t="n">
         <v>22.3164</v>
@@ -4742,19 +4742,19 @@
         <v>115187</v>
       </c>
       <c r="M58" s="16" t="n">
-        <v>36672</v>
+        <v>36819</v>
       </c>
       <c r="N58" s="16" t="n">
         <v>261</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>36933</v>
+        <v>37080</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>78254</v>
+        <v>78107</v>
       </c>
       <c r="Q58" s="16" t="n">
-        <v>78254</v>
+        <v>78107</v>
       </c>
       <c r="R58" s="16" t="n">
         <v>0</v>
@@ -4884,19 +4884,19 @@
         <v>44131</v>
       </c>
       <c r="M60" s="16" t="n">
-        <v>19663</v>
+        <v>21233</v>
       </c>
       <c r="N60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O60" s="16" t="n">
-        <v>19663</v>
+        <v>21233</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>24468</v>
+        <v>22898</v>
       </c>
       <c r="Q60" s="16" t="n">
-        <v>24468</v>
+        <v>22898</v>
       </c>
       <c r="R60" s="16" t="n">
         <v>0</v>
@@ -4955,19 +4955,19 @@
         <v>30118</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>10465</v>
+        <v>12035</v>
       </c>
       <c r="N61" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O61" s="19" t="n">
-        <v>10465</v>
+        <v>12035</v>
       </c>
       <c r="P61" s="19" t="n">
-        <v>19653</v>
+        <v>18083</v>
       </c>
       <c r="Q61" s="19" t="n">
-        <v>19653</v>
+        <v>18083</v>
       </c>
       <c r="R61" s="19" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
         <v>414.286</v>
       </c>
       <c r="M62" s="16" t="n">
-        <v>74.634</v>
+        <v>77.872</v>
       </c>
       <c r="N62" s="16" t="n">
         <v>0.17</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>74.804</v>
+        <v>78.042</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>339.482</v>
+        <v>336.244</v>
       </c>
       <c r="Q62" s="16" t="n">
-        <v>339.482</v>
+        <v>336.244</v>
       </c>
       <c r="R62" s="16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S62" s="15" t="inlineStr"/>
     </row>
@@ -5097,19 +5097,19 @@
         <v>19399</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>11573</v>
+        <v>11622</v>
       </c>
       <c r="N63" s="19" t="n">
         <v>60</v>
       </c>
       <c r="O63" s="19" t="n">
-        <v>11633</v>
+        <v>11682</v>
       </c>
       <c r="P63" s="19" t="n">
-        <v>7766</v>
+        <v>7717</v>
       </c>
       <c r="Q63" s="19" t="n">
-        <v>7766</v>
+        <v>7717</v>
       </c>
       <c r="R63" s="19" t="n">
         <v>0</v>
@@ -5310,19 +5310,19 @@
         <v>38244</v>
       </c>
       <c r="M66" s="16" t="n">
-        <v>26852</v>
+        <v>26901</v>
       </c>
       <c r="N66" s="16" t="n">
         <v>87</v>
       </c>
       <c r="O66" s="16" t="n">
-        <v>26939</v>
+        <v>26988</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>11305</v>
+        <v>11256</v>
       </c>
       <c r="Q66" s="16" t="n">
-        <v>11305</v>
+        <v>11256</v>
       </c>
       <c r="R66" s="16" t="n">
         <v>0</v>
@@ -5381,19 +5381,19 @@
         <v>21.8745</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>13.426</v>
+        <v>13.4505</v>
       </c>
       <c r="N67" s="19" t="n">
         <v>0.0435</v>
       </c>
       <c r="O67" s="19" t="n">
-        <v>13.4695</v>
+        <v>13.494</v>
       </c>
       <c r="P67" s="19" t="n">
-        <v>8.404999999999999</v>
+        <v>8.3805</v>
       </c>
       <c r="Q67" s="19" t="n">
-        <v>8.404999999999999</v>
+        <v>8.3805</v>
       </c>
       <c r="R67" s="19" t="n">
         <v>-0</v>
@@ -5452,19 +5452,19 @@
         <v>188.31</v>
       </c>
       <c r="M68" s="16" t="n">
-        <v>111.784</v>
+        <v>111.98</v>
       </c>
       <c r="N68" s="16" t="n">
         <v>0.348</v>
       </c>
       <c r="O68" s="16" t="n">
-        <v>112.132</v>
+        <v>112.328</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>76.178</v>
+        <v>75.982</v>
       </c>
       <c r="Q68" s="16" t="n">
-        <v>76.178</v>
+        <v>75.982</v>
       </c>
       <c r="R68" s="16" t="n">
         <v>0</v>
@@ -5523,19 +5523,19 @@
         <v>177.8056</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>53.8382</v>
+        <v>58.5402</v>
       </c>
       <c r="N69" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O69" s="19" t="n">
-        <v>53.8382</v>
+        <v>58.5402</v>
       </c>
       <c r="P69" s="19" t="n">
-        <v>123.9674</v>
+        <v>119.2654</v>
       </c>
       <c r="Q69" s="19" t="n">
-        <v>123.9674</v>
+        <v>119.2654</v>
       </c>
       <c r="R69" s="19" t="n">
         <v>0</v>
@@ -5555,58 +5555,58 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Exhaust Raw</t>
+          <t>Ceiling Raw</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>200200027</t>
+          <t>200100031</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>3202010001</t>
+          <t>3101010030</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=22``, W=18``, T=0.025mm)</t>
+          <t>XL/Shaft (Big)-144mm</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J70" s="16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="16" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N70" s="16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O70" s="16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>24.97</v>
+        <v>100</v>
       </c>
       <c r="Q70" s="16" t="n">
-        <v>24.97</v>
+        <v>100</v>
       </c>
       <c r="R70" s="16" t="n">
         <v>0</v>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="D71" s="17" t="inlineStr">
         <is>
-          <t>200200033</t>
+          <t>200200027</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr">
         <is>
-          <t>3202010007</t>
+          <t>3202010001</t>
         </is>
       </c>
       <c r="F71" s="18" t="inlineStr">
         <is>
-          <t>PP Band Fita</t>
+          <t>HDPE Poly (L=22``, W=18``, T=0.025mm)</t>
         </is>
       </c>
       <c r="G71" s="17" t="inlineStr">
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="H71" s="19" t="n">
-        <v>9.954700000000001</v>
+        <v>0</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>28.8</v>
+        <v>25</v>
       </c>
       <c r="J71" s="19" t="n">
         <v>0</v>
@@ -5662,22 +5662,22 @@
         <v>0</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>38.7547</v>
+        <v>25</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>19.6372</v>
+        <v>0</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>19.6372</v>
+        <v>0.03</v>
       </c>
       <c r="P71" s="19" t="n">
-        <v>19.1175</v>
+        <v>24.97</v>
       </c>
       <c r="Q71" s="19" t="n">
-        <v>19.1175</v>
+        <v>24.97</v>
       </c>
       <c r="R71" s="19" t="n">
         <v>0</v>
@@ -5697,34 +5697,34 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Packing Materials - FAN</t>
+          <t>Exhaust Raw</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>300300036</t>
+          <t>200200033</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>3201010036</t>
+          <t>3202010007</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>Blade Carton -Hero (3601)-400x120x29mm</t>
+          <t>PP Band Fita</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="H72" s="16" t="n">
-        <v>0</v>
+        <v>9.954700000000001</v>
       </c>
       <c r="I72" s="16" t="n">
-        <v>8160</v>
+        <v>28.8</v>
       </c>
       <c r="J72" s="16" t="n">
         <v>0</v>
@@ -5733,22 +5733,22 @@
         <v>0</v>
       </c>
       <c r="L72" s="16" t="n">
-        <v>8160</v>
+        <v>38.7547</v>
       </c>
       <c r="M72" s="16" t="n">
-        <v>8107</v>
+        <v>22.9593</v>
       </c>
       <c r="N72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O72" s="16" t="n">
-        <v>8107</v>
+        <v>22.9593</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>53</v>
+        <v>15.7954</v>
       </c>
       <c r="Q72" s="16" t="n">
-        <v>53</v>
+        <v>15.7954</v>
       </c>
       <c r="R72" s="16" t="n">
         <v>0</v>
@@ -5773,17 +5773,17 @@
       </c>
       <c r="D73" s="17" t="inlineStr">
         <is>
-          <t>300300035</t>
+          <t>300300036</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>3201010035</t>
+          <t>3201010036</t>
         </is>
       </c>
       <c r="F73" s="18" t="inlineStr">
         <is>
-          <t>Blade Carton -Popular (4801)-528x144x32mm</t>
+          <t>Blade Carton -Hero (3601)-400x120x29mm</t>
         </is>
       </c>
       <c r="G73" s="17" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="H73" s="19" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>2000</v>
+        <v>8200</v>
       </c>
       <c r="J73" s="19" t="n">
         <v>0</v>
@@ -5804,22 +5804,22 @@
         <v>0</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>2200</v>
+        <v>8200</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>2070</v>
+        <v>8107</v>
       </c>
       <c r="N73" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>2070</v>
+        <v>8107</v>
       </c>
       <c r="P73" s="19" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="Q73" s="19" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="R73" s="19" t="n">
         <v>0</v>
@@ -5844,17 +5844,17 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>300300034</t>
+          <t>300300035</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>3201010034</t>
+          <t>3201010035</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>Blade Carton -Speed king (5602)-622x127x30mm</t>
+          <t>Blade Carton -Popular (4801)-528x144x32mm</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="H74" s="16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I74" s="16" t="n">
-        <v>4414</v>
+        <v>3800</v>
       </c>
       <c r="J74" s="16" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
         <v>0</v>
       </c>
       <c r="L74" s="16" t="n">
-        <v>4414</v>
+        <v>4000</v>
       </c>
       <c r="M74" s="16" t="n">
-        <v>4414</v>
+        <v>3730</v>
       </c>
       <c r="N74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>4414</v>
+        <v>3730</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Q74" s="16" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="R74" s="16" t="n">
         <v>0</v>
@@ -5915,17 +5915,17 @@
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>300300030</t>
+          <t>300300034</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr">
         <is>
-          <t>3201010030</t>
+          <t>3201010034</t>
         </is>
       </c>
       <c r="F75" s="18" t="inlineStr">
         <is>
-          <t>Blade Carton-Premium (5601)-622x153x34mm</t>
+          <t>Blade Carton -Speed king (5602)-622x127x30mm</t>
         </is>
       </c>
       <c r="G75" s="17" t="inlineStr">
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="H75" s="19" t="n">
-        <v>3727</v>
+        <v>0</v>
       </c>
       <c r="I75" s="19" t="n">
-        <v>6203</v>
+        <v>5040</v>
       </c>
       <c r="J75" s="19" t="n">
         <v>0</v>
@@ -5946,22 +5946,22 @@
         <v>0</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>9930</v>
+        <v>5040</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>4250</v>
+        <v>4923</v>
       </c>
       <c r="N75" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O75" s="19" t="n">
-        <v>4250</v>
+        <v>4923</v>
       </c>
       <c r="P75" s="19" t="n">
-        <v>5680</v>
+        <v>117</v>
       </c>
       <c r="Q75" s="19" t="n">
-        <v>5680</v>
+        <v>117</v>
       </c>
       <c r="R75" s="19" t="n">
         <v>0</v>
@@ -5986,17 +5986,17 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>300300031</t>
+          <t>300300030</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>3201010031</t>
+          <t>3201010030</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Blade Carton-Premium Gold (5603)</t>
+          <t>Blade Carton-Premium (5601)-622x153x34mm</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="H76" s="16" t="n">
-        <v>0</v>
+        <v>3727</v>
       </c>
       <c r="I76" s="16" t="n">
-        <v>1800</v>
+        <v>6203</v>
       </c>
       <c r="J76" s="16" t="n">
         <v>0</v>
@@ -6017,22 +6017,22 @@
         <v>0</v>
       </c>
       <c r="L76" s="16" t="n">
-        <v>1800</v>
+        <v>9930</v>
       </c>
       <c r="M76" s="16" t="n">
-        <v>1533</v>
+        <v>5620</v>
       </c>
       <c r="N76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O76" s="16" t="n">
-        <v>1533</v>
+        <v>5620</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>267</v>
+        <v>4310</v>
       </c>
       <c r="Q76" s="16" t="n">
-        <v>267</v>
+        <v>4310</v>
       </c>
       <c r="R76" s="16" t="n">
         <v>0</v>
@@ -6057,17 +6057,17 @@
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
-          <t>300300032</t>
+          <t>300300031</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr">
         <is>
-          <t>3201010032</t>
+          <t>3201010031</t>
         </is>
       </c>
       <c r="F77" s="18" t="inlineStr">
         <is>
-          <t>Blade Carton-Premium Plus (5606)</t>
+          <t>Blade Carton-Premium Gold (5603)</t>
         </is>
       </c>
       <c r="G77" s="17" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="H77" s="19" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="I77" s="19" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J77" s="19" t="n">
         <v>0</v>
@@ -6088,22 +6088,22 @@
         <v>0</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>71</v>
+        <v>1800</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="N77" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O77" s="19" t="n">
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="P77" s="19" t="n">
-        <v>71</v>
+        <v>267</v>
       </c>
       <c r="Q77" s="19" t="n">
-        <v>71</v>
+        <v>267</v>
       </c>
       <c r="R77" s="19" t="n">
         <v>0</v>
@@ -6128,17 +6128,17 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>300300057</t>
+          <t>300300032</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>3201010057</t>
+          <t>3201010032</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>Body Carton - Crown (5607)</t>
+          <t>Blade Carton-Premium Plus (5606)</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="H78" s="16" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I78" s="16" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J78" s="16" t="n">
         <v>0</v>
@@ -6159,22 +6159,22 @@
         <v>0</v>
       </c>
       <c r="L78" s="16" t="n">
-        <v>200</v>
+        <v>71</v>
       </c>
       <c r="M78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="Q78" s="16" t="n">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="R78" s="16" t="n">
         <v>0</v>
@@ -6199,17 +6199,17 @@
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
-          <t>300300028</t>
+          <t>300300057</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr">
         <is>
-          <t>3201010028</t>
+          <t>3201010057</t>
         </is>
       </c>
       <c r="F79" s="18" t="inlineStr">
         <is>
-          <t>Body Carton -Hero (3601)-195x195x230mm</t>
+          <t>Body Carton - Crown (5607)</t>
         </is>
       </c>
       <c r="G79" s="17" t="inlineStr">
@@ -6218,10 +6218,10 @@
         </is>
       </c>
       <c r="H79" s="19" t="n">
-        <v>1593</v>
+        <v>0</v>
       </c>
       <c r="I79" s="19" t="n">
-        <v>5621</v>
+        <v>200</v>
       </c>
       <c r="J79" s="19" t="n">
         <v>0</v>
@@ -6230,22 +6230,22 @@
         <v>0</v>
       </c>
       <c r="L79" s="19" t="n">
-        <v>7214</v>
+        <v>200</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>7150</v>
+        <v>0</v>
       </c>
       <c r="N79" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O79" s="19" t="n">
-        <v>7150</v>
+        <v>2</v>
       </c>
       <c r="P79" s="19" t="n">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="Q79" s="19" t="n">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="R79" s="19" t="n">
         <v>0</v>
@@ -6270,17 +6270,17 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>300300027</t>
+          <t>300300028</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>3201010027</t>
+          <t>3201010028</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>Body Carton -Popular (4801)-264x262x200mm</t>
+          <t>Body Carton -Hero (3601)-195x195x230mm</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="H80" s="16" t="n">
-        <v>97</v>
+        <v>1593</v>
       </c>
       <c r="I80" s="16" t="n">
-        <v>2480</v>
+        <v>5621</v>
       </c>
       <c r="J80" s="16" t="n">
         <v>0</v>
@@ -6301,22 +6301,22 @@
         <v>0</v>
       </c>
       <c r="L80" s="16" t="n">
-        <v>2577</v>
+        <v>7214</v>
       </c>
       <c r="M80" s="16" t="n">
-        <v>2125</v>
+        <v>7150</v>
       </c>
       <c r="N80" s="16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O80" s="16" t="n">
-        <v>2185</v>
+        <v>7150</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>392</v>
+        <v>64</v>
       </c>
       <c r="Q80" s="16" t="n">
-        <v>392</v>
+        <v>64</v>
       </c>
       <c r="R80" s="16" t="n">
         <v>0</v>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
-          <t>300300022</t>
+          <t>300300027</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr">
         <is>
-          <t>3201010022</t>
+          <t>3201010027</t>
         </is>
       </c>
       <c r="F81" s="18" t="inlineStr">
         <is>
-          <t>Body Carton -Premium (5601)-263x264x213mm</t>
+          <t>Body Carton -Popular (4801)-264x262x200mm</t>
         </is>
       </c>
       <c r="G81" s="17" t="inlineStr">
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="H81" s="19" t="n">
-        <v>3107</v>
+        <v>97</v>
       </c>
       <c r="I81" s="19" t="n">
-        <v>13075</v>
+        <v>2480</v>
       </c>
       <c r="J81" s="19" t="n">
         <v>0</v>
@@ -6372,22 +6372,22 @@
         <v>0</v>
       </c>
       <c r="L81" s="19" t="n">
-        <v>16182</v>
+        <v>2577</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>9448</v>
+        <v>2174</v>
       </c>
       <c r="N81" s="19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O81" s="19" t="n">
-        <v>9448</v>
+        <v>2234</v>
       </c>
       <c r="P81" s="19" t="n">
-        <v>6734</v>
+        <v>343</v>
       </c>
       <c r="Q81" s="19" t="n">
-        <v>6734</v>
+        <v>343</v>
       </c>
       <c r="R81" s="19" t="n">
         <v>0</v>
@@ -6412,17 +6412,17 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>300300026</t>
+          <t>300300022</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>3201010026</t>
+          <t>3201010022</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>Body Carton -Speed king (5602) -220x220x208mm</t>
+          <t>Body Carton -Premium (5601)-263x264x213mm</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6431,10 +6431,10 @@
         </is>
       </c>
       <c r="H82" s="16" t="n">
-        <v>85</v>
+        <v>3107</v>
       </c>
       <c r="I82" s="16" t="n">
-        <v>6650</v>
+        <v>15075</v>
       </c>
       <c r="J82" s="16" t="n">
         <v>0</v>
@@ -6443,22 +6443,22 @@
         <v>0</v>
       </c>
       <c r="L82" s="16" t="n">
-        <v>6735</v>
+        <v>18182</v>
       </c>
       <c r="M82" s="16" t="n">
-        <v>5290</v>
+        <v>9448</v>
       </c>
       <c r="N82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="16" t="n">
-        <v>5290</v>
+        <v>9448</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>1445</v>
+        <v>8734</v>
       </c>
       <c r="Q82" s="16" t="n">
-        <v>1445</v>
+        <v>8734</v>
       </c>
       <c r="R82" s="16" t="n">
         <v>0</v>
@@ -6483,17 +6483,17 @@
       </c>
       <c r="D83" s="17" t="inlineStr">
         <is>
-          <t>300300029</t>
+          <t>300300026</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr">
         <is>
-          <t>3201010029</t>
+          <t>3201010026</t>
         </is>
       </c>
       <c r="F83" s="18" t="inlineStr">
         <is>
-          <t>Body Carton -Super (2401)-185x185x267mm</t>
+          <t>Body Carton -Speed king (5602) -220x220x208mm</t>
         </is>
       </c>
       <c r="G83" s="17" t="inlineStr">
@@ -6502,10 +6502,10 @@
         </is>
       </c>
       <c r="H83" s="19" t="n">
-        <v>2150</v>
+        <v>85</v>
       </c>
       <c r="I83" s="19" t="n">
-        <v>40</v>
+        <v>6650</v>
       </c>
       <c r="J83" s="19" t="n">
         <v>0</v>
@@ -6514,22 +6514,22 @@
         <v>0</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>2190</v>
+        <v>6735</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>2188</v>
+        <v>5290</v>
       </c>
       <c r="N83" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="19" t="n">
-        <v>2188</v>
+        <v>5290</v>
       </c>
       <c r="P83" s="19" t="n">
-        <v>2</v>
+        <v>1445</v>
       </c>
       <c r="Q83" s="19" t="n">
-        <v>2</v>
+        <v>1445</v>
       </c>
       <c r="R83" s="19" t="n">
         <v>0</v>
@@ -6554,17 +6554,17 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>300300023</t>
+          <t>300300029</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>3201010023</t>
+          <t>3201010029</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>Body Carton Premium Gold (5603)</t>
+          <t>Body Carton -Super (2401)-185x185x267mm</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="H84" s="16" t="n">
-        <v>0</v>
+        <v>2150</v>
       </c>
       <c r="I84" s="16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="J84" s="16" t="n">
         <v>0</v>
@@ -6585,22 +6585,22 @@
         <v>0</v>
       </c>
       <c r="L84" s="16" t="n">
-        <v>1000</v>
+        <v>2190</v>
       </c>
       <c r="M84" s="16" t="n">
-        <v>651</v>
+        <v>2188</v>
       </c>
       <c r="N84" s="16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O84" s="16" t="n">
-        <v>676</v>
+        <v>2188</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>324</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="16" t="n">
-        <v>324</v>
+        <v>2</v>
       </c>
       <c r="R84" s="16" t="n">
         <v>0</v>
@@ -6625,17 +6625,17 @@
       </c>
       <c r="D85" s="17" t="inlineStr">
         <is>
-          <t>300300024</t>
+          <t>300300023</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr">
         <is>
-          <t>3201010024</t>
+          <t>3201010023</t>
         </is>
       </c>
       <c r="F85" s="18" t="inlineStr">
         <is>
-          <t>Body Carton Premium Plus (5606)</t>
+          <t>Body Carton Premium Gold (5603)</t>
         </is>
       </c>
       <c r="G85" s="17" t="inlineStr">
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="H85" s="19" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="I85" s="19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J85" s="19" t="n">
         <v>0</v>
@@ -6656,22 +6656,22 @@
         <v>0</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>273</v>
+        <v>1000</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="N85" s="19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O85" s="19" t="n">
-        <v>0</v>
+        <v>676</v>
       </c>
       <c r="P85" s="19" t="n">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="Q85" s="19" t="n">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="R85" s="19" t="n">
         <v>0</v>
@@ -6696,17 +6696,17 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>300300051</t>
+          <t>300300024</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>3201010051</t>
+          <t>3201010024</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>Body Sticker - 5603</t>
+          <t>Body Carton Premium Plus (5606)</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="H86" s="16" t="n">
-        <v>765</v>
+        <v>273</v>
       </c>
       <c r="I86" s="16" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="J86" s="16" t="n">
         <v>0</v>
@@ -6727,22 +6727,22 @@
         <v>0</v>
       </c>
       <c r="L86" s="16" t="n">
-        <v>5265</v>
+        <v>273</v>
       </c>
       <c r="M86" s="16" t="n">
-        <v>651</v>
+        <v>0</v>
       </c>
       <c r="N86" s="16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O86" s="16" t="n">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>4589</v>
+        <v>273</v>
       </c>
       <c r="Q86" s="16" t="n">
-        <v>4589</v>
+        <v>273</v>
       </c>
       <c r="R86" s="16" t="n">
         <v>0</v>
@@ -6767,17 +6767,17 @@
       </c>
       <c r="D87" s="17" t="inlineStr">
         <is>
-          <t>300300059</t>
+          <t>300300051</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
-          <t>3201010059</t>
+          <t>3201010051</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
         <is>
-          <t>Body Sticker (5607)</t>
+          <t>Body Sticker - 5603</t>
         </is>
       </c>
       <c r="G87" s="17" t="inlineStr">
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="H87" s="19" t="n">
-        <v>200</v>
+        <v>765</v>
       </c>
       <c r="I87" s="19" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="J87" s="19" t="n">
         <v>0</v>
@@ -6798,22 +6798,22 @@
         <v>0</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>200</v>
+        <v>5265</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="N87" s="19" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="O87" s="19" t="n">
-        <v>2</v>
+        <v>676</v>
       </c>
       <c r="P87" s="19" t="n">
-        <v>198</v>
+        <v>4589</v>
       </c>
       <c r="Q87" s="19" t="n">
-        <v>198</v>
+        <v>4589</v>
       </c>
       <c r="R87" s="19" t="n">
         <v>0</v>
@@ -6838,17 +6838,17 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>300300006</t>
+          <t>300300059</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>3201010006</t>
+          <t>3201010059</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>Body Sticker Speed King</t>
+          <t>Body Sticker (5607)</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="H88" s="16" t="n">
-        <v>717</v>
+        <v>200</v>
       </c>
       <c r="I88" s="16" t="n">
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="J88" s="16" t="n">
         <v>0</v>
@@ -6869,22 +6869,22 @@
         <v>0</v>
       </c>
       <c r="L88" s="16" t="n">
-        <v>5967</v>
+        <v>200</v>
       </c>
       <c r="M88" s="16" t="n">
-        <v>5290</v>
+        <v>0</v>
       </c>
       <c r="N88" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O88" s="16" t="n">
-        <v>5290</v>
+        <v>2</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>677</v>
+        <v>198</v>
       </c>
       <c r="Q88" s="16" t="n">
-        <v>677</v>
+        <v>198</v>
       </c>
       <c r="R88" s="16" t="n">
         <v>0</v>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D89" s="17" t="inlineStr">
         <is>
-          <t>300300009</t>
+          <t>300300006</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr">
         <is>
-          <t>3201010009</t>
+          <t>3201010006</t>
         </is>
       </c>
       <c r="F89" s="18" t="inlineStr">
         <is>
-          <t>Body Sticker-2401</t>
+          <t>Body Sticker Speed King</t>
         </is>
       </c>
       <c r="G89" s="17" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="H89" s="19" t="n">
-        <v>5370</v>
+        <v>717</v>
       </c>
       <c r="I89" s="19" t="n">
-        <v>0</v>
+        <v>5250</v>
       </c>
       <c r="J89" s="19" t="n">
         <v>0</v>
@@ -6940,22 +6940,22 @@
         <v>0</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>5370</v>
+        <v>5967</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>2188</v>
+        <v>5290</v>
       </c>
       <c r="N89" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="19" t="n">
-        <v>2188</v>
+        <v>5290</v>
       </c>
       <c r="P89" s="19" t="n">
-        <v>3182</v>
+        <v>677</v>
       </c>
       <c r="Q89" s="19" t="n">
-        <v>3182</v>
+        <v>677</v>
       </c>
       <c r="R89" s="19" t="n">
         <v>0</v>
@@ -6980,17 +6980,17 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>300300008</t>
+          <t>300300009</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>3201010008</t>
+          <t>3201010009</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>Body Sticker-3601</t>
+          <t>Body Sticker-2401</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="H90" s="16" t="n">
-        <v>2143</v>
+        <v>5370</v>
       </c>
       <c r="I90" s="16" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="J90" s="16" t="n">
         <v>0</v>
@@ -7011,22 +7011,22 @@
         <v>0</v>
       </c>
       <c r="L90" s="16" t="n">
-        <v>8643</v>
+        <v>5370</v>
       </c>
       <c r="M90" s="16" t="n">
-        <v>7150</v>
+        <v>2188</v>
       </c>
       <c r="N90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="16" t="n">
-        <v>7150</v>
+        <v>2188</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>1493</v>
+        <v>3182</v>
       </c>
       <c r="Q90" s="16" t="n">
-        <v>1493</v>
+        <v>3182</v>
       </c>
       <c r="R90" s="16" t="n">
         <v>0</v>
@@ -7051,17 +7051,17 @@
       </c>
       <c r="D91" s="17" t="inlineStr">
         <is>
-          <t>300300007</t>
+          <t>300300008</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr">
         <is>
-          <t>3201010007</t>
+          <t>3201010008</t>
         </is>
       </c>
       <c r="F91" s="18" t="inlineStr">
         <is>
-          <t>Body Sticker-4801</t>
+          <t>Body Sticker-3601</t>
         </is>
       </c>
       <c r="G91" s="17" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="H91" s="19" t="n">
-        <v>3278</v>
+        <v>2143</v>
       </c>
       <c r="I91" s="19" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="J91" s="19" t="n">
         <v>0</v>
@@ -7082,22 +7082,22 @@
         <v>0</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>3278</v>
+        <v>8643</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>2125</v>
+        <v>7150</v>
       </c>
       <c r="N91" s="19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O91" s="19" t="n">
-        <v>2185</v>
+        <v>7150</v>
       </c>
       <c r="P91" s="19" t="n">
-        <v>1093</v>
+        <v>1493</v>
       </c>
       <c r="Q91" s="19" t="n">
-        <v>1093</v>
+        <v>1493</v>
       </c>
       <c r="R91" s="19" t="n">
         <v>0</v>
@@ -7122,17 +7122,17 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>300300004</t>
+          <t>300300007</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>3201010004</t>
+          <t>3201010007</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>Body Sticker-5601</t>
+          <t>Body Sticker-4801</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="H92" s="16" t="n">
-        <v>9158</v>
+        <v>3278</v>
       </c>
       <c r="I92" s="16" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="J92" s="16" t="n">
         <v>0</v>
@@ -7153,22 +7153,22 @@
         <v>0</v>
       </c>
       <c r="L92" s="16" t="n">
-        <v>39158</v>
+        <v>3278</v>
       </c>
       <c r="M92" s="16" t="n">
-        <v>9448</v>
+        <v>2174</v>
       </c>
       <c r="N92" s="16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O92" s="16" t="n">
-        <v>9448</v>
+        <v>2234</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>29710</v>
+        <v>1044</v>
       </c>
       <c r="Q92" s="16" t="n">
-        <v>29710</v>
+        <v>1044</v>
       </c>
       <c r="R92" s="16" t="n">
         <v>0</v>
@@ -7193,17 +7193,17 @@
       </c>
       <c r="D93" s="17" t="inlineStr">
         <is>
-          <t>300300005</t>
+          <t>300300004</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr">
         <is>
-          <t>3201010005</t>
+          <t>3201010004</t>
         </is>
       </c>
       <c r="F93" s="18" t="inlineStr">
         <is>
-          <t>Body Sticker-Premium Plus(5606)</t>
+          <t>Body Sticker-5601</t>
         </is>
       </c>
       <c r="G93" s="17" t="inlineStr">
@@ -7212,10 +7212,10 @@
         </is>
       </c>
       <c r="H93" s="19" t="n">
-        <v>868</v>
+        <v>9158</v>
       </c>
       <c r="I93" s="19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="J93" s="19" t="n">
         <v>0</v>
@@ -7224,22 +7224,22 @@
         <v>0</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>868</v>
+        <v>39158</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>0</v>
+        <v>9448</v>
       </c>
       <c r="N93" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="19" t="n">
-        <v>0</v>
+        <v>9448</v>
       </c>
       <c r="P93" s="19" t="n">
-        <v>868</v>
+        <v>29710</v>
       </c>
       <c r="Q93" s="19" t="n">
-        <v>868</v>
+        <v>29710</v>
       </c>
       <c r="R93" s="19" t="n">
         <v>0</v>
@@ -7264,17 +7264,17 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>300300011</t>
+          <t>300300005</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>3201010011</t>
+          <t>3201010005</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>Canopy Sticker Speed King</t>
+          <t>Body Sticker-Premium Plus(5606)</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="H94" s="16" t="n">
-        <v>7572</v>
+        <v>868</v>
       </c>
       <c r="I94" s="16" t="n">
         <v>0</v>
@@ -7295,22 +7295,22 @@
         <v>0</v>
       </c>
       <c r="L94" s="16" t="n">
-        <v>7572</v>
+        <v>868</v>
       </c>
       <c r="M94" s="16" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="N94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>3972</v>
+        <v>868</v>
       </c>
       <c r="Q94" s="16" t="n">
-        <v>3972</v>
+        <v>868</v>
       </c>
       <c r="R94" s="16" t="n">
         <v>0</v>
@@ -7335,29 +7335,29 @@
       </c>
       <c r="D95" s="17" t="inlineStr">
         <is>
-          <t>300300046</t>
+          <t>300300011</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr">
         <is>
-          <t>3201010046</t>
+          <t>3201010011</t>
         </is>
       </c>
       <c r="F95" s="18" t="inlineStr">
         <is>
-          <t>Carton Tape - (W=60mm,L=200m, MEP Print)</t>
+          <t>Canopy Sticker Speed King</t>
         </is>
       </c>
       <c r="G95" s="17" t="inlineStr">
         <is>
-          <t>Mtr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H95" s="19" t="n">
-        <v>13093.2</v>
+        <v>7572</v>
       </c>
       <c r="I95" s="19" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="J95" s="19" t="n">
         <v>0</v>
@@ -7366,25 +7366,25 @@
         <v>0</v>
       </c>
       <c r="L95" s="19" t="n">
-        <v>43093.2</v>
+        <v>7572</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>25452.4</v>
+        <v>3600</v>
       </c>
       <c r="N95" s="19" t="n">
-        <v>69.8</v>
+        <v>0</v>
       </c>
       <c r="O95" s="19" t="n">
-        <v>25522.2</v>
+        <v>3600</v>
       </c>
       <c r="P95" s="19" t="n">
-        <v>17571</v>
+        <v>3972</v>
       </c>
       <c r="Q95" s="19" t="n">
-        <v>17571</v>
+        <v>3972</v>
       </c>
       <c r="R95" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S95" s="18" t="inlineStr"/>
     </row>
@@ -7406,29 +7406,29 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>300300061</t>
+          <t>300300046</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>3201010061</t>
+          <t>3201010046</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>Cork Sheet - 5607</t>
+          <t>Carton Tape - (W=60mm,L=200m, MEP Print)</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Mtr</t>
         </is>
       </c>
       <c r="H96" s="16" t="n">
-        <v>29</v>
+        <v>13093.2</v>
       </c>
       <c r="I96" s="16" t="n">
-        <v>200</v>
+        <v>30000</v>
       </c>
       <c r="J96" s="16" t="n">
         <v>0</v>
@@ -7437,22 +7437,22 @@
         <v>0</v>
       </c>
       <c r="L96" s="16" t="n">
-        <v>229</v>
+        <v>43093.2</v>
       </c>
       <c r="M96" s="16" t="n">
-        <v>0</v>
+        <v>27280.6</v>
       </c>
       <c r="N96" s="16" t="n">
-        <v>2</v>
+        <v>69.8</v>
       </c>
       <c r="O96" s="16" t="n">
-        <v>2</v>
+        <v>27350.4</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>227</v>
+        <v>15742.8</v>
       </c>
       <c r="Q96" s="16" t="n">
-        <v>227</v>
+        <v>15742.8</v>
       </c>
       <c r="R96" s="16" t="n">
         <v>0</v>
@@ -7477,17 +7477,17 @@
       </c>
       <c r="D97" s="17" t="inlineStr">
         <is>
-          <t>300300021</t>
+          <t>300300061</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr">
         <is>
-          <t>3201010021</t>
+          <t>3201010061</t>
         </is>
       </c>
       <c r="F97" s="18" t="inlineStr">
         <is>
-          <t>Cork Sheet -2401/3601</t>
+          <t>Cork Sheet - 5607</t>
         </is>
       </c>
       <c r="G97" s="17" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="H97" s="19" t="n">
-        <v>5947</v>
+        <v>29</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>3480</v>
+        <v>200</v>
       </c>
       <c r="J97" s="19" t="n">
         <v>0</v>
@@ -7508,22 +7508,22 @@
         <v>0</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>9427</v>
+        <v>229</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>9338</v>
+        <v>0</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>9338</v>
+        <v>2</v>
       </c>
       <c r="P97" s="19" t="n">
-        <v>89</v>
+        <v>227</v>
       </c>
       <c r="Q97" s="19" t="n">
-        <v>89</v>
+        <v>227</v>
       </c>
       <c r="R97" s="19" t="n">
         <v>0</v>
@@ -7548,17 +7548,17 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>300300019</t>
+          <t>300300021</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>3201010019</t>
+          <t>3201010021</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>Cork Sheet -5601````/4801````</t>
+          <t>Cork Sheet -2401/3601</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="H98" s="16" t="n">
-        <v>6022</v>
+        <v>5947</v>
       </c>
       <c r="I98" s="16" t="n">
-        <v>11100</v>
+        <v>3480</v>
       </c>
       <c r="J98" s="16" t="n">
         <v>0</v>
@@ -7579,22 +7579,22 @@
         <v>0</v>
       </c>
       <c r="L98" s="16" t="n">
-        <v>17122</v>
+        <v>9427</v>
       </c>
       <c r="M98" s="16" t="n">
-        <v>12224</v>
+        <v>9338</v>
       </c>
       <c r="N98" s="16" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>12309</v>
+        <v>9338</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>4813</v>
+        <v>89</v>
       </c>
       <c r="Q98" s="16" t="n">
-        <v>4813</v>
+        <v>89</v>
       </c>
       <c r="R98" s="16" t="n">
         <v>0</v>
@@ -7619,17 +7619,17 @@
       </c>
       <c r="D99" s="17" t="inlineStr">
         <is>
-          <t>300300020</t>
+          <t>300300019</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr">
         <is>
-          <t>3201010020</t>
+          <t>3201010019</t>
         </is>
       </c>
       <c r="F99" s="18" t="inlineStr">
         <is>
-          <t>Cork Sheet -5602````</t>
+          <t>Cork Sheet -5601````/4801````</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr">
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="H99" s="19" t="n">
-        <v>10</v>
+        <v>6022</v>
       </c>
       <c r="I99" s="19" t="n">
-        <v>5280</v>
+        <v>11100</v>
       </c>
       <c r="J99" s="19" t="n">
         <v>0</v>
@@ -7650,22 +7650,22 @@
         <v>0</v>
       </c>
       <c r="L99" s="19" t="n">
-        <v>5290</v>
+        <v>17122</v>
       </c>
       <c r="M99" s="19" t="n">
-        <v>5290</v>
+        <v>12273</v>
       </c>
       <c r="N99" s="19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O99" s="19" t="n">
-        <v>5290</v>
+        <v>12358</v>
       </c>
       <c r="P99" s="19" t="n">
-        <v>0</v>
+        <v>4764</v>
       </c>
       <c r="Q99" s="19" t="n">
-        <v>0</v>
+        <v>4764</v>
       </c>
       <c r="R99" s="19" t="n">
         <v>0</v>
@@ -7690,17 +7690,17 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>300300010</t>
+          <t>300300020</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>3201010010</t>
+          <t>3201010020</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
-          <t>Fan Canopy Sticker</t>
+          <t>Cork Sheet -5602````</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="H100" s="16" t="n">
-        <v>38606</v>
+        <v>10</v>
       </c>
       <c r="I100" s="16" t="n">
-        <v>52000</v>
+        <v>5280</v>
       </c>
       <c r="J100" s="16" t="n">
         <v>0</v>
@@ -7721,22 +7721,22 @@
         <v>0</v>
       </c>
       <c r="L100" s="16" t="n">
-        <v>90606</v>
+        <v>5290</v>
       </c>
       <c r="M100" s="16" t="n">
-        <v>42024</v>
+        <v>5290</v>
       </c>
       <c r="N100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="16" t="n">
-        <v>42024</v>
+        <v>5290</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>48582</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="16" t="n">
-        <v>48582</v>
+        <v>0</v>
       </c>
       <c r="R100" s="16" t="n">
         <v>0</v>
@@ -7761,17 +7761,17 @@
       </c>
       <c r="D101" s="17" t="inlineStr">
         <is>
-          <t>300300013</t>
+          <t>300300010</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
-          <t>3201010013</t>
+          <t>3201010010</t>
         </is>
       </c>
       <c r="F101" s="18" t="inlineStr">
         <is>
-          <t>Fan Down Pipe Sticker</t>
+          <t>Fan Canopy Sticker</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="H101" s="19" t="n">
-        <v>14695</v>
+        <v>38606</v>
       </c>
       <c r="I101" s="19" t="n">
-        <v>37500</v>
+        <v>52000</v>
       </c>
       <c r="J101" s="19" t="n">
         <v>0</v>
@@ -7792,22 +7792,22 @@
         <v>0</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>52195</v>
+        <v>90606</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>10465</v>
+        <v>43824</v>
       </c>
       <c r="N101" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O101" s="19" t="n">
-        <v>10465</v>
+        <v>43824</v>
       </c>
       <c r="P101" s="19" t="n">
-        <v>41730</v>
+        <v>46782</v>
       </c>
       <c r="Q101" s="19" t="n">
-        <v>41730</v>
+        <v>46782</v>
       </c>
       <c r="R101" s="19" t="n">
         <v>0</v>
@@ -7832,17 +7832,17 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>300300014</t>
+          <t>300300013</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>3201010014</t>
+          <t>3201010013</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>Fan QC Sticker</t>
+          <t>Fan Down Pipe Sticker</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="H102" s="16" t="n">
-        <v>33742</v>
+        <v>14695</v>
       </c>
       <c r="I102" s="16" t="n">
-        <v>0</v>
+        <v>37500</v>
       </c>
       <c r="J102" s="16" t="n">
         <v>0</v>
@@ -7863,22 +7863,22 @@
         <v>0</v>
       </c>
       <c r="L102" s="16" t="n">
-        <v>33742</v>
+        <v>52195</v>
       </c>
       <c r="M102" s="16" t="n">
-        <v>26852</v>
+        <v>12035</v>
       </c>
       <c r="N102" s="16" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="O102" s="16" t="n">
-        <v>26939</v>
+        <v>12035</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>6803</v>
+        <v>40160</v>
       </c>
       <c r="Q102" s="16" t="n">
-        <v>6803</v>
+        <v>40160</v>
       </c>
       <c r="R102" s="16" t="n">
         <v>0</v>
@@ -7903,17 +7903,17 @@
       </c>
       <c r="D103" s="17" t="inlineStr">
         <is>
-          <t>300300002</t>
+          <t>300300014</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr">
         <is>
-          <t>3201010002</t>
+          <t>3201010014</t>
         </is>
       </c>
       <c r="F103" s="18" t="inlineStr">
         <is>
-          <t>FAN Shank Paper</t>
+          <t>Fan QC Sticker</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr">
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="H103" s="19" t="n">
-        <v>21680</v>
+        <v>33742</v>
       </c>
       <c r="I103" s="19" t="n">
-        <v>70000</v>
+        <v>20000</v>
       </c>
       <c r="J103" s="19" t="n">
         <v>0</v>
@@ -7934,22 +7934,22 @@
         <v>0</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>91680</v>
+        <v>53742</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>61122</v>
+        <v>26901</v>
       </c>
       <c r="N103" s="19" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="O103" s="19" t="n">
-        <v>61122</v>
+        <v>26988</v>
       </c>
       <c r="P103" s="19" t="n">
-        <v>30558</v>
+        <v>26754</v>
       </c>
       <c r="Q103" s="19" t="n">
-        <v>30558</v>
+        <v>26754</v>
       </c>
       <c r="R103" s="19" t="n">
         <v>0</v>
@@ -7974,17 +7974,17 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>300300054</t>
+          <t>300300002</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>3201010054</t>
+          <t>3201010002</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>Fan Without Regulator Sticker</t>
+          <t>FAN Shank Paper</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="H104" s="16" t="n">
-        <v>11812</v>
+        <v>21680</v>
       </c>
       <c r="I104" s="16" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="J104" s="16" t="n">
         <v>0</v>
@@ -8005,22 +8005,22 @@
         <v>0</v>
       </c>
       <c r="L104" s="16" t="n">
-        <v>11812</v>
+        <v>91680</v>
       </c>
       <c r="M104" s="16" t="n">
-        <v>0</v>
+        <v>71739</v>
       </c>
       <c r="N104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O104" s="16" t="n">
-        <v>0</v>
+        <v>71739</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>11812</v>
+        <v>19941</v>
       </c>
       <c r="Q104" s="16" t="n">
-        <v>11812</v>
+        <v>19941</v>
       </c>
       <c r="R104" s="16" t="n">
         <v>0</v>
@@ -8045,17 +8045,17 @@
       </c>
       <c r="D105" s="17" t="inlineStr">
         <is>
-          <t>300300060</t>
+          <t>300300054</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr">
         <is>
-          <t>3201010060</t>
+          <t>3201010054</t>
         </is>
       </c>
       <c r="F105" s="18" t="inlineStr">
         <is>
-          <t>Guarantee Card - Crown (5607)</t>
+          <t>Fan Without Regulator Sticker</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr">
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="H105" s="19" t="n">
-        <v>434</v>
+        <v>11812</v>
       </c>
       <c r="I105" s="19" t="n">
         <v>0</v>
@@ -8076,22 +8076,22 @@
         <v>0</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>434</v>
+        <v>11812</v>
       </c>
       <c r="M105" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N105" s="19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O105" s="19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P105" s="19" t="n">
-        <v>432</v>
+        <v>11812</v>
       </c>
       <c r="Q105" s="19" t="n">
-        <v>432</v>
+        <v>11812</v>
       </c>
       <c r="R105" s="19" t="n">
         <v>0</v>
@@ -8116,17 +8116,17 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>300300018</t>
+          <t>300300060</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>3201010018</t>
+          <t>3201010060</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>Guarantee Card -2401,3601</t>
+          <t>Guarantee Card - Crown (5607)</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="H106" s="16" t="n">
-        <v>6986</v>
+        <v>434</v>
       </c>
       <c r="I106" s="16" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J106" s="16" t="n">
         <v>0</v>
@@ -8147,22 +8147,22 @@
         <v>0</v>
       </c>
       <c r="L106" s="16" t="n">
-        <v>12986</v>
+        <v>434</v>
       </c>
       <c r="M106" s="16" t="n">
-        <v>9338</v>
+        <v>0</v>
       </c>
       <c r="N106" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O106" s="16" t="n">
-        <v>9338</v>
+        <v>2</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>3648</v>
+        <v>432</v>
       </c>
       <c r="Q106" s="16" t="n">
-        <v>3648</v>
+        <v>432</v>
       </c>
       <c r="R106" s="16" t="n">
         <v>0</v>
@@ -8187,17 +8187,17 @@
       </c>
       <c r="D107" s="17" t="inlineStr">
         <is>
-          <t>300300016</t>
+          <t>300300018</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr">
         <is>
-          <t>3201010016</t>
+          <t>3201010018</t>
         </is>
       </c>
       <c r="F107" s="18" t="inlineStr">
         <is>
-          <t>Guarantee Card -4801</t>
+          <t>Guarantee Card -2401,3601</t>
         </is>
       </c>
       <c r="G107" s="17" t="inlineStr">
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="H107" s="19" t="n">
-        <v>3801</v>
+        <v>6986</v>
       </c>
       <c r="I107" s="19" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="J107" s="19" t="n">
         <v>0</v>
@@ -8218,22 +8218,22 @@
         <v>0</v>
       </c>
       <c r="L107" s="19" t="n">
-        <v>3801</v>
+        <v>12986</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>2125</v>
+        <v>9338</v>
       </c>
       <c r="N107" s="19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O107" s="19" t="n">
-        <v>2185</v>
+        <v>9338</v>
       </c>
       <c r="P107" s="19" t="n">
-        <v>1616</v>
+        <v>3648</v>
       </c>
       <c r="Q107" s="19" t="n">
-        <v>1616</v>
+        <v>3648</v>
       </c>
       <c r="R107" s="19" t="n">
         <v>0</v>
@@ -8258,17 +8258,17 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>300300015</t>
+          <t>300300016</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>3201010015</t>
+          <t>3201010016</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>Guarantee Card -5601</t>
+          <t>Guarantee Card -4801</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -8277,10 +8277,10 @@
         </is>
       </c>
       <c r="H108" s="16" t="n">
-        <v>15367</v>
+        <v>3801</v>
       </c>
       <c r="I108" s="16" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="J108" s="16" t="n">
         <v>0</v>
@@ -8289,22 +8289,22 @@
         <v>0</v>
       </c>
       <c r="L108" s="16" t="n">
-        <v>30367</v>
+        <v>3801</v>
       </c>
       <c r="M108" s="16" t="n">
-        <v>9448</v>
+        <v>2174</v>
       </c>
       <c r="N108" s="16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O108" s="16" t="n">
-        <v>9448</v>
+        <v>2234</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>20919</v>
+        <v>1567</v>
       </c>
       <c r="Q108" s="16" t="n">
-        <v>20919</v>
+        <v>1567</v>
       </c>
       <c r="R108" s="16" t="n">
         <v>0</v>
@@ -8329,17 +8329,17 @@
       </c>
       <c r="D109" s="17" t="inlineStr">
         <is>
-          <t>300300064</t>
+          <t>300300015</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr">
         <is>
-          <t>3201010064</t>
+          <t>3201010015</t>
         </is>
       </c>
       <c r="F109" s="18" t="inlineStr">
         <is>
-          <t>Guarantee Card -5603</t>
+          <t>Guarantee Card -5601</t>
         </is>
       </c>
       <c r="G109" s="17" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="H109" s="19" t="n">
-        <v>694</v>
+        <v>15367</v>
       </c>
       <c r="I109" s="19" t="n">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="J109" s="19" t="n">
         <v>0</v>
@@ -8360,22 +8360,22 @@
         <v>0</v>
       </c>
       <c r="L109" s="19" t="n">
-        <v>3694</v>
+        <v>30367</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>651</v>
+        <v>9448</v>
       </c>
       <c r="N109" s="19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O109" s="19" t="n">
-        <v>676</v>
+        <v>9448</v>
       </c>
       <c r="P109" s="19" t="n">
-        <v>3018</v>
+        <v>20919</v>
       </c>
       <c r="Q109" s="19" t="n">
-        <v>3018</v>
+        <v>20919</v>
       </c>
       <c r="R109" s="19" t="n">
         <v>0</v>
@@ -8400,17 +8400,17 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>300300017</t>
+          <t>300300064</t>
         </is>
       </c>
       <c r="E110" s="15" t="inlineStr">
         <is>
-          <t>3201010017</t>
+          <t>3201010064</t>
         </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>Guarantee Card Speed King</t>
+          <t>Guarantee Card -5603</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H110" s="16" t="n">
-        <v>787</v>
+        <v>694</v>
       </c>
       <c r="I110" s="16" t="n">
-        <v>11200</v>
+        <v>3000</v>
       </c>
       <c r="J110" s="16" t="n">
         <v>0</v>
@@ -8431,22 +8431,22 @@
         <v>0</v>
       </c>
       <c r="L110" s="16" t="n">
-        <v>11987</v>
+        <v>3694</v>
       </c>
       <c r="M110" s="16" t="n">
-        <v>5290</v>
+        <v>651</v>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O110" s="16" t="n">
-        <v>5290</v>
+        <v>676</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>6697</v>
+        <v>3018</v>
       </c>
       <c r="Q110" s="16" t="n">
-        <v>6697</v>
+        <v>3018</v>
       </c>
       <c r="R110" s="16" t="n">
         <v>0</v>
@@ -8471,29 +8471,29 @@
       </c>
       <c r="D111" s="17" t="inlineStr">
         <is>
-          <t>300300042</t>
+          <t>300300017</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>3201010042</t>
+          <t>3201010017</t>
         </is>
       </c>
       <c r="F111" s="18" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=13``, W=4``, T=0.035mm)</t>
+          <t>Guarantee Card Speed King</t>
         </is>
       </c>
       <c r="G111" s="17" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H111" s="19" t="n">
-        <v>42.468</v>
+        <v>787</v>
       </c>
       <c r="I111" s="19" t="n">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="J111" s="19" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
         <v>0</v>
       </c>
       <c r="L111" s="19" t="n">
-        <v>272.595</v>
+        <v>11987</v>
       </c>
       <c r="M111" s="19" t="n">
-        <v>55.497</v>
+        <v>5290</v>
       </c>
       <c r="N111" s="19" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="O111" s="19" t="n">
-        <v>55.503</v>
+        <v>5290</v>
       </c>
       <c r="P111" s="19" t="n">
-        <v>217.092</v>
+        <v>6697</v>
       </c>
       <c r="Q111" s="19" t="n">
-        <v>217.092</v>
+        <v>6697</v>
       </c>
       <c r="R111" s="19" t="n">
         <v>0</v>
@@ -8542,17 +8542,17 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>300300038</t>
+          <t>300300042</t>
         </is>
       </c>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>3201010038</t>
+          <t>3201010042</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=14``, W=12``,T=0.035mm)</t>
+          <t>HDPE Poly (L=13``, W=4``, T=0.035mm)</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="H112" s="16" t="n">
-        <v>96.34</v>
+        <v>42.468</v>
       </c>
       <c r="I112" s="16" t="n">
         <v>0</v>
@@ -8573,22 +8573,22 @@
         <v>0</v>
       </c>
       <c r="L112" s="16" t="n">
-        <v>270.43</v>
+        <v>272.595</v>
       </c>
       <c r="M112" s="16" t="n">
-        <v>93.38</v>
+        <v>64.227</v>
       </c>
       <c r="N112" s="16" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>93.38</v>
+        <v>64.233</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>177.05</v>
+        <v>208.362</v>
       </c>
       <c r="Q112" s="16" t="n">
-        <v>177.05</v>
+        <v>208.362</v>
       </c>
       <c r="R112" s="16" t="n">
         <v>0</v>
@@ -8613,17 +8613,17 @@
       </c>
       <c r="D113" s="17" t="inlineStr">
         <is>
-          <t>300300037</t>
+          <t>300300038</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr">
         <is>
-          <t>3201010037</t>
+          <t>3201010038</t>
         </is>
       </c>
       <c r="F113" s="18" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=15``, W=15``, T=0.035mm)</t>
+          <t>HDPE Poly (L=14``, W=12``,T=0.035mm)</t>
         </is>
       </c>
       <c r="G113" s="17" t="inlineStr">
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="H113" s="19" t="n">
-        <v>57.177</v>
+        <v>96.34</v>
       </c>
       <c r="I113" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J113" s="19" t="n">
         <v>0</v>
@@ -8644,22 +8644,22 @@
         <v>0</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>440.078</v>
+        <v>270.43</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>191.01</v>
+        <v>93.38</v>
       </c>
       <c r="N113" s="19" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O113" s="19" t="n">
-        <v>191.86</v>
+        <v>93.38</v>
       </c>
       <c r="P113" s="19" t="n">
-        <v>248.218</v>
+        <v>177.05</v>
       </c>
       <c r="Q113" s="19" t="n">
-        <v>248.218</v>
+        <v>177.05</v>
       </c>
       <c r="R113" s="19" t="n">
         <v>0</v>
@@ -8684,17 +8684,17 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>300300040</t>
+          <t>300300037</t>
         </is>
       </c>
       <c r="E114" s="15" t="inlineStr">
         <is>
-          <t>3201010040</t>
+          <t>3201010037</t>
         </is>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=18``, W=7``, T=0.035mm)</t>
+          <t>HDPE Poly (L=15``, W=15``, T=0.035mm)</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="H114" s="16" t="n">
-        <v>7.58</v>
+        <v>57.177</v>
       </c>
       <c r="I114" s="16" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J114" s="16" t="n">
         <v>0</v>
@@ -8715,25 +8715,25 @@
         <v>0</v>
       </c>
       <c r="L114" s="16" t="n">
-        <v>280</v>
+        <v>440.078</v>
       </c>
       <c r="M114" s="16" t="n">
-        <v>64.85599999999999</v>
+        <v>191.5</v>
       </c>
       <c r="N114" s="16" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="O114" s="16" t="n">
-        <v>64.85599999999999</v>
+        <v>192.35</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>215.144</v>
+        <v>247.728</v>
       </c>
       <c r="Q114" s="16" t="n">
-        <v>215.144</v>
+        <v>247.728</v>
       </c>
       <c r="R114" s="16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S114" s="15" t="inlineStr"/>
     </row>
@@ -8755,17 +8755,17 @@
       </c>
       <c r="D115" s="17" t="inlineStr">
         <is>
-          <t>300300039</t>
+          <t>300300040</t>
         </is>
       </c>
       <c r="E115" s="18" t="inlineStr">
         <is>
-          <t>3201010039</t>
+          <t>3201010040</t>
         </is>
       </c>
       <c r="F115" s="18" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=27``, W=8``, T=0.035mm)</t>
+          <t>HDPE Poly (L=18``, W=7``, T=0.035mm)</t>
         </is>
       </c>
       <c r="G115" s="17" t="inlineStr">
@@ -8774,10 +8774,10 @@
         </is>
       </c>
       <c r="H115" s="19" t="n">
-        <v>64.90900000000001</v>
+        <v>7.58</v>
       </c>
       <c r="I115" s="19" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J115" s="19" t="n">
         <v>0</v>
@@ -8786,22 +8786,22 @@
         <v>0</v>
       </c>
       <c r="L115" s="19" t="n">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="M115" s="19" t="n">
-        <v>108.233</v>
+        <v>64.85599999999999</v>
       </c>
       <c r="N115" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="19" t="n">
-        <v>108.233</v>
+        <v>64.85599999999999</v>
       </c>
       <c r="P115" s="19" t="n">
-        <v>150.767</v>
+        <v>215.144</v>
       </c>
       <c r="Q115" s="19" t="n">
-        <v>150.767</v>
+        <v>215.144</v>
       </c>
       <c r="R115" s="19" t="n">
         <v>0</v>
@@ -8826,17 +8826,17 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>300300041</t>
+          <t>300300039</t>
         </is>
       </c>
       <c r="E116" s="15" t="inlineStr">
         <is>
-          <t>3201010041</t>
+          <t>3201010039</t>
         </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=9``, W=9``, T=0.025mm)</t>
+          <t>HDPE Poly (L=27``, W=8``, T=0.035mm)</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="H116" s="16" t="n">
-        <v>39.665</v>
+        <v>64.90900000000001</v>
       </c>
       <c r="I116" s="16" t="n">
         <v>150</v>
@@ -8857,22 +8857,22 @@
         <v>0</v>
       </c>
       <c r="L116" s="16" t="n">
-        <v>217.868</v>
+        <v>259</v>
       </c>
       <c r="M116" s="16" t="n">
-        <v>68.43600000000001</v>
+        <v>138.424</v>
       </c>
       <c r="N116" s="16" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O116" s="16" t="n">
-        <v>68.44799999999999</v>
+        <v>138.424</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>149.42</v>
+        <v>120.576</v>
       </c>
       <c r="Q116" s="16" t="n">
-        <v>149.42</v>
+        <v>120.576</v>
       </c>
       <c r="R116" s="16" t="n">
         <v>0</v>
@@ -8897,29 +8897,29 @@
       </c>
       <c r="D117" s="17" t="inlineStr">
         <is>
-          <t>200200030</t>
+          <t>300300041</t>
         </is>
       </c>
       <c r="E117" s="18" t="inlineStr">
         <is>
-          <t>3201010062</t>
+          <t>3201010041</t>
         </is>
       </c>
       <c r="F117" s="18" t="inlineStr">
         <is>
-          <t>MEP Hologram Sticker</t>
+          <t>HDPE Poly (L=9``, W=9``, T=0.025mm)</t>
         </is>
       </c>
       <c r="G117" s="17" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="H117" s="19" t="n">
-        <v>18335</v>
+        <v>39.665</v>
       </c>
       <c r="I117" s="19" t="n">
-        <v>21600</v>
+        <v>150</v>
       </c>
       <c r="J117" s="19" t="n">
         <v>0</v>
@@ -8928,25 +8928,25 @@
         <v>0</v>
       </c>
       <c r="L117" s="19" t="n">
-        <v>39935</v>
+        <v>217.868</v>
       </c>
       <c r="M117" s="19" t="n">
-        <v>21562</v>
+        <v>71.136</v>
       </c>
       <c r="N117" s="19" t="n">
-        <v>87</v>
+        <v>0.012</v>
       </c>
       <c r="O117" s="19" t="n">
-        <v>21649</v>
+        <v>71.148</v>
       </c>
       <c r="P117" s="19" t="n">
-        <v>18286</v>
+        <v>146.72</v>
       </c>
       <c r="Q117" s="19" t="n">
-        <v>17906</v>
+        <v>146.72</v>
       </c>
       <c r="R117" s="19" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="S117" s="18" t="inlineStr"/>
     </row>
@@ -8968,29 +8968,29 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>300300043</t>
+          <t>200200030</t>
         </is>
       </c>
       <c r="E118" s="15" t="inlineStr">
         <is>
-          <t>3201010043</t>
+          <t>3201010062</t>
         </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>PP Poly (L=5``, W=5``, T=0.045mm) With Logo Print</t>
+          <t>MEP Hologram Sticker</t>
         </is>
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H118" s="16" t="n">
-        <v>63.82148</v>
+        <v>18335</v>
       </c>
       <c r="I118" s="16" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="J118" s="16" t="n">
         <v>0</v>
@@ -8999,25 +8999,25 @@
         <v>0</v>
       </c>
       <c r="L118" s="16" t="n">
-        <v>63.82148</v>
+        <v>39935</v>
       </c>
       <c r="M118" s="16" t="n">
-        <v>17.78088</v>
+        <v>21611</v>
       </c>
       <c r="N118" s="16" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="O118" s="16" t="n">
-        <v>17.78088</v>
+        <v>21698</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>46.0406</v>
+        <v>18237</v>
       </c>
       <c r="Q118" s="16" t="n">
-        <v>42.2191</v>
+        <v>17857</v>
       </c>
       <c r="R118" s="16" t="n">
-        <v>3.8215</v>
+        <v>380</v>
       </c>
       <c r="S118" s="15" t="inlineStr"/>
     </row>
@@ -9039,17 +9039,17 @@
       </c>
       <c r="D119" s="17" t="inlineStr">
         <is>
-          <t>300300053</t>
+          <t>300300043</t>
         </is>
       </c>
       <c r="E119" s="18" t="inlineStr">
         <is>
-          <t>3201010053</t>
+          <t>3201010043</t>
         </is>
       </c>
       <c r="F119" s="18" t="inlineStr">
         <is>
-          <t>Roll Poly - 4``</t>
+          <t>PP Poly (L=5``, W=5``, T=0.045mm) With Logo Print</t>
         </is>
       </c>
       <c r="G119" s="17" t="inlineStr">
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="H119" s="19" t="n">
-        <v>80.6361</v>
+        <v>63.82148</v>
       </c>
       <c r="I119" s="19" t="n">
         <v>0</v>
@@ -9070,25 +9070,25 @@
         <v>0</v>
       </c>
       <c r="L119" s="19" t="n">
-        <v>80.6361</v>
+        <v>63.82148</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>1.44</v>
+        <v>18.22368</v>
       </c>
       <c r="N119" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O119" s="19" t="n">
-        <v>1.44</v>
+        <v>18.22368</v>
       </c>
       <c r="P119" s="19" t="n">
-        <v>79.1961</v>
+        <v>45.5978</v>
       </c>
       <c r="Q119" s="19" t="n">
-        <v>79.1961</v>
+        <v>41.7763</v>
       </c>
       <c r="R119" s="19" t="n">
-        <v>0</v>
+        <v>3.8215</v>
       </c>
       <c r="S119" s="18" t="inlineStr"/>
     </row>
@@ -9110,29 +9110,29 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>300300052</t>
+          <t>300300053</t>
         </is>
       </c>
       <c r="E120" s="15" t="inlineStr">
         <is>
-          <t>3201010052</t>
+          <t>3201010053</t>
         </is>
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>Speed King Hologram Sticker</t>
+          <t>Roll Poly - 4``</t>
         </is>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="H120" s="16" t="n">
-        <v>5103</v>
+        <v>80.6361</v>
       </c>
       <c r="I120" s="16" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J120" s="16" t="n">
         <v>0</v>
@@ -9141,25 +9141,25 @@
         <v>0</v>
       </c>
       <c r="L120" s="16" t="n">
-        <v>15103</v>
+        <v>80.6361</v>
       </c>
       <c r="M120" s="16" t="n">
-        <v>5290</v>
+        <v>1.44</v>
       </c>
       <c r="N120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O120" s="16" t="n">
-        <v>5290</v>
+        <v>1.44</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>9813</v>
+        <v>79.1961</v>
       </c>
       <c r="Q120" s="16" t="n">
-        <v>9511</v>
+        <v>79.1961</v>
       </c>
       <c r="R120" s="16" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="S120" s="15" t="inlineStr"/>
     </row>
@@ -9181,17 +9181,17 @@
       </c>
       <c r="D121" s="17" t="inlineStr">
         <is>
-          <t>300300003</t>
+          <t>300300052</t>
         </is>
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
-          <t>3201010003</t>
+          <t>3201010052</t>
         </is>
       </c>
       <c r="F121" s="18" t="inlineStr">
         <is>
-          <t>Tissue Paper</t>
+          <t>Speed King Hologram Sticker</t>
         </is>
       </c>
       <c r="G121" s="17" t="inlineStr">
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="H121" s="19" t="n">
-        <v>13783.28</v>
+        <v>5103</v>
       </c>
       <c r="I121" s="19" t="n">
-        <v>46200</v>
+        <v>10000</v>
       </c>
       <c r="J121" s="19" t="n">
         <v>0</v>
@@ -9212,25 +9212,25 @@
         <v>0</v>
       </c>
       <c r="L121" s="19" t="n">
-        <v>59983.38</v>
+        <v>15103</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>30445.68</v>
+        <v>5290</v>
       </c>
       <c r="N121" s="19" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="O121" s="19" t="n">
-        <v>30491.88</v>
+        <v>5290</v>
       </c>
       <c r="P121" s="19" t="n">
-        <v>29491.5</v>
+        <v>9813</v>
       </c>
       <c r="Q121" s="19" t="n">
-        <v>29491.5</v>
+        <v>9511</v>
       </c>
       <c r="R121" s="19" t="n">
-        <v>-0</v>
+        <v>302</v>
       </c>
       <c r="S121" s="18" t="inlineStr"/>
     </row>
@@ -9252,17 +9252,17 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>300300056</t>
+          <t>300300003</t>
         </is>
       </c>
       <c r="E122" s="15" t="inlineStr">
         <is>
-          <t>3201010056</t>
+          <t>3201010003</t>
         </is>
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
-          <t>With Gang Regulator Sticker</t>
+          <t>Tissue Paper</t>
         </is>
       </c>
       <c r="G122" s="14" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="H122" s="16" t="n">
-        <v>1463</v>
+        <v>13783.28</v>
       </c>
       <c r="I122" s="16" t="n">
-        <v>0</v>
+        <v>46200</v>
       </c>
       <c r="J122" s="16" t="n">
         <v>0</v>
@@ -9283,25 +9283,25 @@
         <v>0</v>
       </c>
       <c r="L122" s="16" t="n">
-        <v>1463</v>
+        <v>59983.38</v>
       </c>
       <c r="M122" s="16" t="n">
-        <v>0</v>
+        <v>34010.16</v>
       </c>
       <c r="N122" s="16" t="n">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="O122" s="16" t="n">
-        <v>0</v>
+        <v>34056.36</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>1463</v>
+        <v>25927.02</v>
       </c>
       <c r="Q122" s="16" t="n">
-        <v>1463</v>
+        <v>25927.02</v>
       </c>
       <c r="R122" s="16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S122" s="15" t="inlineStr"/>
     </row>
@@ -9318,34 +9318,34 @@
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>Production Consumables - FAN</t>
+          <t>Packing Materials - FAN</t>
         </is>
       </c>
       <c r="D123" s="17" t="inlineStr">
         <is>
-          <t>700100038</t>
+          <t>300300056</t>
         </is>
       </c>
       <c r="E123" s="18" t="inlineStr">
         <is>
-          <t>700100039</t>
+          <t>3201010056</t>
         </is>
       </c>
       <c r="F123" s="18" t="inlineStr">
         <is>
-          <t>Carton Tape Transparent- (W=57mm,L=200m, Non Print)</t>
+          <t>With Gang Regulator Sticker</t>
         </is>
       </c>
       <c r="G123" s="17" t="inlineStr">
         <is>
-          <t>Mtr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H123" s="19" t="n">
-        <v>0</v>
+        <v>1463</v>
       </c>
       <c r="I123" s="19" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="J123" s="19" t="n">
         <v>0</v>
@@ -9354,22 +9354,22 @@
         <v>0</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>2400</v>
+        <v>1463</v>
       </c>
       <c r="M123" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N123" s="19" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="O123" s="19" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P123" s="19" t="n">
-        <v>0</v>
+        <v>1463</v>
       </c>
       <c r="Q123" s="19" t="n">
-        <v>0</v>
+        <v>1463</v>
       </c>
       <c r="R123" s="19" t="n">
         <v>0</v>
@@ -9394,29 +9394,29 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>700100003</t>
+          <t>700100038</t>
         </is>
       </c>
       <c r="E124" s="15" t="inlineStr">
         <is>
-          <t>700000003</t>
+          <t>700100039</t>
         </is>
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>Hands Gloves - Cotton</t>
+          <t>Carton Tape Transparent- (W=57mm,L=200m, Non Print)</t>
         </is>
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Mtr</t>
         </is>
       </c>
       <c r="H124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="16" t="n">
-        <v>552</v>
+        <v>2400</v>
       </c>
       <c r="J124" s="16" t="n">
         <v>0</v>
@@ -9425,22 +9425,22 @@
         <v>0</v>
       </c>
       <c r="L124" s="16" t="n">
-        <v>552</v>
+        <v>2400</v>
       </c>
       <c r="M124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N124" s="16" t="n">
-        <v>300</v>
+        <v>2400</v>
       </c>
       <c r="O124" s="16" t="n">
-        <v>300</v>
+        <v>2400</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="16" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="R124" s="16" t="n">
         <v>0</v>
@@ -9465,17 +9465,17 @@
       </c>
       <c r="D125" s="17" t="inlineStr">
         <is>
-          <t>700100031</t>
+          <t>700100003</t>
         </is>
       </c>
       <c r="E125" s="18" t="inlineStr">
         <is>
-          <t>700100032</t>
+          <t>700000003</t>
         </is>
       </c>
       <c r="F125" s="18" t="inlineStr">
         <is>
-          <t>Thermal QR Code sticker Roll 38 mm x 25 mm</t>
+          <t>Hands Gloves - Cotton</t>
         </is>
       </c>
       <c r="G125" s="17" t="inlineStr">
@@ -9487,7 +9487,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="19" t="n">
-        <v>43000</v>
+        <v>552</v>
       </c>
       <c r="J125" s="19" t="n">
         <v>0</v>
@@ -9496,22 +9496,22 @@
         <v>0</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>43000</v>
+        <v>552</v>
       </c>
       <c r="M125" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N125" s="19" t="n">
-        <v>30000</v>
+        <v>300</v>
       </c>
       <c r="O125" s="19" t="n">
-        <v>30000</v>
+        <v>300</v>
       </c>
       <c r="P125" s="19" t="n">
-        <v>13000</v>
+        <v>252</v>
       </c>
       <c r="Q125" s="19" t="n">
-        <v>13000</v>
+        <v>252</v>
       </c>
       <c r="R125" s="19" t="n">
         <v>0</v>
@@ -9531,34 +9531,34 @@
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>FAN SFG</t>
+          <t>Production Consumables - FAN</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>1300100071</t>
+          <t>700100031</t>
         </is>
       </c>
       <c r="E126" s="15" t="inlineStr">
         <is>
-          <t>SFG1010071</t>
+          <t>700100032</t>
         </is>
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
-          <t>2401 Super Ceiling Fan Blade - Ivory</t>
+          <t>Thermal QR Code sticker Roll 38 mm x 25 mm</t>
         </is>
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H126" s="16" t="n">
-        <v>4768</v>
+        <v>0</v>
       </c>
       <c r="I126" s="16" t="n">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="J126" s="16" t="n">
         <v>0</v>
@@ -9567,22 +9567,22 @@
         <v>0</v>
       </c>
       <c r="L126" s="16" t="n">
-        <v>4768</v>
+        <v>43000</v>
       </c>
       <c r="M126" s="16" t="n">
-        <v>2188</v>
+        <v>0</v>
       </c>
       <c r="N126" s="16" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="O126" s="16" t="n">
-        <v>2188</v>
+        <v>38000</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>2580</v>
+        <v>5000</v>
       </c>
       <c r="Q126" s="16" t="n">
-        <v>2580</v>
+        <v>5000</v>
       </c>
       <c r="R126" s="16" t="n">
         <v>0</v>
@@ -9607,26 +9607,26 @@
       </c>
       <c r="D127" s="17" t="inlineStr">
         <is>
-          <t>1300100076</t>
+          <t>1300100071</t>
         </is>
       </c>
       <c r="E127" s="18" t="inlineStr">
         <is>
-          <t>SFG1010076</t>
+          <t>SFG1010071</t>
         </is>
       </c>
       <c r="F127" s="18" t="inlineStr">
         <is>
-          <t>2401 Super Ceiling Fan Complete Body - Ivory</t>
+          <t>2401 Super Ceiling Fan Blade - Ivory</t>
         </is>
       </c>
       <c r="G127" s="17" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H127" s="19" t="n">
-        <v>0</v>
+        <v>4768</v>
       </c>
       <c r="I127" s="19" t="n">
         <v>0</v>
@@ -9635,10 +9635,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="19" t="n">
-        <v>2188</v>
+        <v>0</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>2188</v>
+        <v>4768</v>
       </c>
       <c r="M127" s="19" t="n">
         <v>2188</v>
@@ -9650,10 +9650,10 @@
         <v>2188</v>
       </c>
       <c r="P127" s="19" t="n">
-        <v>0</v>
+        <v>2580</v>
       </c>
       <c r="Q127" s="19" t="n">
-        <v>0</v>
+        <v>2580</v>
       </c>
       <c r="R127" s="19" t="n">
         <v>0</v>
@@ -9678,26 +9678,26 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>1300100072</t>
+          <t>1300100076</t>
         </is>
       </c>
       <c r="E128" s="15" t="inlineStr">
         <is>
-          <t>SFG1010072</t>
+          <t>SFG1010076</t>
         </is>
       </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
-          <t>3601 Hero Ceiling Fan Blade - Ivory</t>
+          <t>2401 Super Ceiling Fan Complete Body - Ivory</t>
         </is>
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H128" s="16" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="I128" s="16" t="n">
         <v>0</v>
@@ -9706,25 +9706,25 @@
         <v>0</v>
       </c>
       <c r="K128" s="16" t="n">
-        <v>8107</v>
+        <v>2188</v>
       </c>
       <c r="L128" s="16" t="n">
-        <v>8468</v>
+        <v>2188</v>
       </c>
       <c r="M128" s="16" t="n">
-        <v>7612</v>
+        <v>2188</v>
       </c>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O128" s="16" t="n">
-        <v>7612</v>
+        <v>2188</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="Q128" s="16" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="R128" s="16" t="n">
         <v>0</v>
@@ -9749,26 +9749,26 @@
       </c>
       <c r="D129" s="17" t="inlineStr">
         <is>
-          <t>1300100077</t>
+          <t>1300100072</t>
         </is>
       </c>
       <c r="E129" s="18" t="inlineStr">
         <is>
-          <t>SFG1010077</t>
+          <t>SFG1010072</t>
         </is>
       </c>
       <c r="F129" s="18" t="inlineStr">
         <is>
-          <t>3601 Hero Ceiling Fan Complete Body - Ivory</t>
+          <t>3601 Hero Ceiling Fan Blade - Ivory</t>
         </is>
       </c>
       <c r="G129" s="17" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H129" s="19" t="n">
-        <v>452</v>
+        <v>361</v>
       </c>
       <c r="I129" s="19" t="n">
         <v>0</v>
@@ -9777,25 +9777,25 @@
         <v>0</v>
       </c>
       <c r="K129" s="19" t="n">
-        <v>7150</v>
+        <v>8107</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>7602</v>
+        <v>8468</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>7602</v>
+        <v>7612</v>
       </c>
       <c r="N129" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O129" s="19" t="n">
-        <v>7602</v>
+        <v>7612</v>
       </c>
       <c r="P129" s="19" t="n">
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q129" s="19" t="n">
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="R129" s="19" t="n">
         <v>0</v>
@@ -9820,26 +9820,26 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>1300100073</t>
+          <t>1300100077</t>
         </is>
       </c>
       <c r="E130" s="15" t="inlineStr">
         <is>
-          <t>SFG1010073</t>
+          <t>SFG1010077</t>
         </is>
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
-          <t>4801 Popular Ceiling Fan Blade - Ivory</t>
+          <t>3601 Hero Ceiling Fan Complete Body - Ivory</t>
         </is>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H130" s="16" t="n">
-        <v>223</v>
+        <v>452</v>
       </c>
       <c r="I130" s="16" t="n">
         <v>0</v>
@@ -9848,25 +9848,25 @@
         <v>0</v>
       </c>
       <c r="K130" s="16" t="n">
-        <v>2070</v>
+        <v>7150</v>
       </c>
       <c r="L130" s="16" t="n">
-        <v>2293</v>
+        <v>7602</v>
       </c>
       <c r="M130" s="16" t="n">
-        <v>2193</v>
+        <v>7602</v>
       </c>
       <c r="N130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O130" s="16" t="n">
-        <v>2193</v>
+        <v>7602</v>
       </c>
       <c r="P130" s="16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q130" s="16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R130" s="16" t="n">
         <v>0</v>
@@ -9891,26 +9891,26 @@
       </c>
       <c r="D131" s="17" t="inlineStr">
         <is>
-          <t>1300100078</t>
+          <t>1300100073</t>
         </is>
       </c>
       <c r="E131" s="18" t="inlineStr">
         <is>
-          <t>SFG1010078</t>
+          <t>SFG1010073</t>
         </is>
       </c>
       <c r="F131" s="18" t="inlineStr">
         <is>
-          <t>4801 Popular Ceiling Fan Complete Body - Ivory</t>
+          <t>4801 Popular Ceiling Fan Blade - Ivory</t>
         </is>
       </c>
       <c r="G131" s="17" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H131" s="19" t="n">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="I131" s="19" t="n">
         <v>0</v>
@@ -9919,25 +9919,25 @@
         <v>0</v>
       </c>
       <c r="K131" s="19" t="n">
-        <v>2125</v>
+        <v>3730</v>
       </c>
       <c r="L131" s="19" t="n">
-        <v>2282</v>
+        <v>3953</v>
       </c>
       <c r="M131" s="19" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="N131" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O131" s="19" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="P131" s="19" t="n">
-        <v>89</v>
+        <v>1622</v>
       </c>
       <c r="Q131" s="19" t="n">
-        <v>89</v>
+        <v>1622</v>
       </c>
       <c r="R131" s="19" t="n">
         <v>0</v>
@@ -9962,26 +9962,26 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>1300100074</t>
+          <t>1300100078</t>
         </is>
       </c>
       <c r="E132" s="15" t="inlineStr">
         <is>
-          <t>SFG1010074</t>
+          <t>SFG1010078</t>
         </is>
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
-          <t>5601 Premium Ceiling Fan Blade - Ivory</t>
+          <t>4801 Popular Ceiling Fan Complete Body - Ivory</t>
         </is>
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H132" s="16" t="n">
-        <v>4880</v>
+        <v>157</v>
       </c>
       <c r="I132" s="16" t="n">
         <v>0</v>
@@ -9990,25 +9990,25 @@
         <v>0</v>
       </c>
       <c r="K132" s="16" t="n">
-        <v>4150</v>
+        <v>2174</v>
       </c>
       <c r="L132" s="16" t="n">
-        <v>9030</v>
+        <v>2331</v>
       </c>
       <c r="M132" s="16" t="n">
-        <v>8756</v>
+        <v>2331</v>
       </c>
       <c r="N132" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O132" s="16" t="n">
-        <v>8756</v>
+        <v>2331</v>
       </c>
       <c r="P132" s="16" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="Q132" s="16" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="R132" s="16" t="n">
         <v>0</v>
@@ -10033,17 +10033,17 @@
       </c>
       <c r="D133" s="17" t="inlineStr">
         <is>
-          <t>1300100111</t>
+          <t>1300100074</t>
         </is>
       </c>
       <c r="E133" s="18" t="inlineStr">
         <is>
-          <t>SFG1010109</t>
+          <t>SFG1010074</t>
         </is>
       </c>
       <c r="F133" s="18" t="inlineStr">
         <is>
-          <t>5601 Premium Ceiling Fan Blade - White</t>
+          <t>5601 Premium Ceiling Fan Blade - Ivory</t>
         </is>
       </c>
       <c r="G133" s="17" t="inlineStr">
@@ -10052,7 +10052,7 @@
         </is>
       </c>
       <c r="H133" s="19" t="n">
-        <v>114</v>
+        <v>4880</v>
       </c>
       <c r="I133" s="19" t="n">
         <v>0</v>
@@ -10061,25 +10061,25 @@
         <v>0</v>
       </c>
       <c r="K133" s="19" t="n">
-        <v>100</v>
+        <v>5520</v>
       </c>
       <c r="L133" s="19" t="n">
-        <v>214</v>
+        <v>10400</v>
       </c>
       <c r="M133" s="19" t="n">
-        <v>33</v>
+        <v>9556</v>
       </c>
       <c r="N133" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O133" s="19" t="n">
-        <v>33</v>
+        <v>9556</v>
       </c>
       <c r="P133" s="19" t="n">
-        <v>181</v>
+        <v>844</v>
       </c>
       <c r="Q133" s="19" t="n">
-        <v>181</v>
+        <v>844</v>
       </c>
       <c r="R133" s="19" t="n">
         <v>0</v>
@@ -10104,26 +10104,26 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>1300100079</t>
+          <t>1300100111</t>
         </is>
       </c>
       <c r="E134" s="15" t="inlineStr">
         <is>
-          <t>SFG1010079</t>
+          <t>SFG1010109</t>
         </is>
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>5601 Premium Ceiling Fan Complete Body - Ivory</t>
+          <t>5601 Premium Ceiling Fan Blade - White</t>
         </is>
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H134" s="16" t="n">
-        <v>2300</v>
+        <v>114</v>
       </c>
       <c r="I134" s="16" t="n">
         <v>0</v>
@@ -10132,25 +10132,25 @@
         <v>0</v>
       </c>
       <c r="K134" s="16" t="n">
-        <v>9415</v>
+        <v>100</v>
       </c>
       <c r="L134" s="16" t="n">
-        <v>11715</v>
+        <v>214</v>
       </c>
       <c r="M134" s="16" t="n">
-        <v>8580</v>
+        <v>33</v>
       </c>
       <c r="N134" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O134" s="16" t="n">
-        <v>8580</v>
+        <v>33</v>
       </c>
       <c r="P134" s="16" t="n">
-        <v>3135</v>
+        <v>181</v>
       </c>
       <c r="Q134" s="16" t="n">
-        <v>3135</v>
+        <v>181</v>
       </c>
       <c r="R134" s="16" t="n">
         <v>0</v>
@@ -10175,17 +10175,17 @@
       </c>
       <c r="D135" s="17" t="inlineStr">
         <is>
-          <t>1300100113</t>
+          <t>1300100079</t>
         </is>
       </c>
       <c r="E135" s="18" t="inlineStr">
         <is>
-          <t>SFG1010116</t>
+          <t>SFG1010079</t>
         </is>
       </c>
       <c r="F135" s="18" t="inlineStr">
         <is>
-          <t>5601 Premium Ceiling Fan Complete Body - Ivory (W.R.)</t>
+          <t>5601 Premium Ceiling Fan Complete Body - Ivory</t>
         </is>
       </c>
       <c r="G135" s="17" t="inlineStr">
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="H135" s="19" t="n">
-        <v>4068</v>
+        <v>2300</v>
       </c>
       <c r="I135" s="19" t="n">
         <v>0</v>
@@ -10203,25 +10203,25 @@
         <v>0</v>
       </c>
       <c r="K135" s="19" t="n">
-        <v>0</v>
+        <v>9415</v>
       </c>
       <c r="L135" s="19" t="n">
-        <v>4068</v>
+        <v>11715</v>
       </c>
       <c r="M135" s="19" t="n">
-        <v>176</v>
+        <v>9380</v>
       </c>
       <c r="N135" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O135" s="19" t="n">
-        <v>176</v>
+        <v>9380</v>
       </c>
       <c r="P135" s="19" t="n">
-        <v>3892</v>
+        <v>2335</v>
       </c>
       <c r="Q135" s="19" t="n">
-        <v>3892</v>
+        <v>2335</v>
       </c>
       <c r="R135" s="19" t="n">
         <v>0</v>
@@ -10246,17 +10246,17 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>1300100106</t>
+          <t>1300100113</t>
         </is>
       </c>
       <c r="E136" s="15" t="inlineStr">
         <is>
-          <t>SFG1010111</t>
+          <t>SFG1010116</t>
         </is>
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
-          <t>5601 Premium Ceiling Fan Complete Body-White</t>
+          <t>5601 Premium Ceiling Fan Complete Body - Ivory (W.R.)</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="H136" s="16" t="n">
-        <v>0</v>
+        <v>4068</v>
       </c>
       <c r="I136" s="16" t="n">
         <v>0</v>
@@ -10274,25 +10274,25 @@
         <v>0</v>
       </c>
       <c r="K136" s="16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L136" s="16" t="n">
-        <v>33</v>
+        <v>4068</v>
       </c>
       <c r="M136" s="16" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O136" s="16" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="P136" s="16" t="n">
-        <v>0</v>
+        <v>3892</v>
       </c>
       <c r="Q136" s="16" t="n">
-        <v>0</v>
+        <v>3892</v>
       </c>
       <c r="R136" s="16" t="n">
         <v>0</v>
@@ -10317,26 +10317,26 @@
       </c>
       <c r="D137" s="17" t="inlineStr">
         <is>
-          <t>1300100075</t>
+          <t>1300100106</t>
         </is>
       </c>
       <c r="E137" s="18" t="inlineStr">
         <is>
-          <t>SFG1010075</t>
+          <t>SFG1010111</t>
         </is>
       </c>
       <c r="F137" s="18" t="inlineStr">
         <is>
-          <t>5602 Speed King Ceiling Fan Blade - Ivory</t>
+          <t>5601 Premium Ceiling Fan Complete Body-White</t>
         </is>
       </c>
       <c r="G137" s="17" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H137" s="19" t="n">
-        <v>1090</v>
+        <v>0</v>
       </c>
       <c r="I137" s="19" t="n">
         <v>0</v>
@@ -10345,25 +10345,25 @@
         <v>0</v>
       </c>
       <c r="K137" s="19" t="n">
-        <v>4414</v>
+        <v>33</v>
       </c>
       <c r="L137" s="19" t="n">
-        <v>5504</v>
+        <v>33</v>
       </c>
       <c r="M137" s="19" t="n">
-        <v>5500</v>
+        <v>33</v>
       </c>
       <c r="N137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O137" s="19" t="n">
-        <v>5500</v>
+        <v>33</v>
       </c>
       <c r="P137" s="19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q137" s="19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R137" s="19" t="n">
         <v>0</v>
@@ -10388,26 +10388,26 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>1300100080</t>
+          <t>1300100075</t>
         </is>
       </c>
       <c r="E138" s="15" t="inlineStr">
         <is>
-          <t>SFG1010080</t>
+          <t>SFG1010075</t>
         </is>
       </c>
       <c r="F138" s="15" t="inlineStr">
         <is>
-          <t>5602 Speed King Ceiling Fan Complete Body - Ivory</t>
+          <t>5602 Speed King Ceiling Fan Blade - Ivory</t>
         </is>
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H138" s="16" t="n">
-        <v>271</v>
+        <v>1090</v>
       </c>
       <c r="I138" s="16" t="n">
         <v>0</v>
@@ -10416,25 +10416,25 @@
         <v>0</v>
       </c>
       <c r="K138" s="16" t="n">
-        <v>5290</v>
+        <v>4923</v>
       </c>
       <c r="L138" s="16" t="n">
-        <v>5561</v>
+        <v>6013</v>
       </c>
       <c r="M138" s="16" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="N138" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O138" s="16" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="P138" s="16" t="n">
-        <v>61</v>
+        <v>460</v>
       </c>
       <c r="Q138" s="16" t="n">
-        <v>61</v>
+        <v>460</v>
       </c>
       <c r="R138" s="16" t="n">
         <v>0</v>
@@ -10459,26 +10459,26 @@
       </c>
       <c r="D139" s="17" t="inlineStr">
         <is>
-          <t>1300100091</t>
+          <t>1300100080</t>
         </is>
       </c>
       <c r="E139" s="18" t="inlineStr">
         <is>
-          <t>SFG1010096</t>
+          <t>SFG1010080</t>
         </is>
       </c>
       <c r="F139" s="18" t="inlineStr">
         <is>
-          <t>5603 Premium Gold Ceiling Fan Blade - Ivory</t>
+          <t>5602 Speed King Ceiling Fan Complete Body - Ivory</t>
         </is>
       </c>
       <c r="G139" s="17" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H139" s="19" t="n">
-        <v>5</v>
+        <v>271</v>
       </c>
       <c r="I139" s="19" t="n">
         <v>0</v>
@@ -10487,25 +10487,25 @@
         <v>0</v>
       </c>
       <c r="K139" s="19" t="n">
-        <v>1533</v>
+        <v>5290</v>
       </c>
       <c r="L139" s="19" t="n">
-        <v>1538</v>
+        <v>5561</v>
       </c>
       <c r="M139" s="19" t="n">
-        <v>1063</v>
+        <v>5553</v>
       </c>
       <c r="N139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O139" s="19" t="n">
-        <v>1063</v>
+        <v>5553</v>
       </c>
       <c r="P139" s="19" t="n">
-        <v>475</v>
+        <v>8</v>
       </c>
       <c r="Q139" s="19" t="n">
-        <v>475</v>
+        <v>8</v>
       </c>
       <c r="R139" s="19" t="n">
         <v>0</v>
@@ -10530,26 +10530,26 @@
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>1300100092</t>
+          <t>1300100091</t>
         </is>
       </c>
       <c r="E140" s="15" t="inlineStr">
         <is>
-          <t>SFG1010097</t>
+          <t>SFG1010096</t>
         </is>
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>5603 Premium Gold Complete Body - Ivory</t>
+          <t>5603 Premium Gold Ceiling Fan Blade - Ivory</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H140" s="16" t="n">
-        <v>411</v>
+        <v>5</v>
       </c>
       <c r="I140" s="16" t="n">
         <v>0</v>
@@ -10558,25 +10558,25 @@
         <v>0</v>
       </c>
       <c r="K140" s="16" t="n">
-        <v>651</v>
+        <v>1533</v>
       </c>
       <c r="L140" s="16" t="n">
-        <v>1062</v>
+        <v>1538</v>
       </c>
       <c r="M140" s="16" t="n">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="N140" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O140" s="16" t="n">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="P140" s="16" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="Q140" s="16" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="R140" s="16" t="n">
         <v>0</v>
@@ -10601,26 +10601,26 @@
       </c>
       <c r="D141" s="17" t="inlineStr">
         <is>
-          <t>1300100136</t>
+          <t>1300100092</t>
         </is>
       </c>
       <c r="E141" s="18" t="inlineStr">
         <is>
-          <t>SFG1010139</t>
+          <t>SFG1010097</t>
         </is>
       </c>
       <c r="F141" s="18" t="inlineStr">
         <is>
-          <t>5606 Premium Plus Ceiling Fan Blade - Ivory</t>
+          <t>5603 Premium Gold Complete Body - Ivory</t>
         </is>
       </c>
       <c r="G141" s="17" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H141" s="19" t="n">
-        <v>254</v>
+        <v>411</v>
       </c>
       <c r="I141" s="19" t="n">
         <v>0</v>
@@ -10629,25 +10629,25 @@
         <v>0</v>
       </c>
       <c r="K141" s="19" t="n">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="L141" s="19" t="n">
-        <v>254</v>
+        <v>1062</v>
       </c>
       <c r="M141" s="19" t="n">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="N141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O141" s="19" t="n">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="P141" s="19" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="Q141" s="19" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="R141" s="19" t="n">
         <v>0</v>
@@ -10672,17 +10672,17 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>1300100133</t>
+          <t>1300100136</t>
         </is>
       </c>
       <c r="E142" s="15" t="inlineStr">
         <is>
-          <t>SFG1010136</t>
+          <t>SFG1010139</t>
         </is>
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
-          <t>5607 Crown Ceiling Fan Blade - Ivory</t>
+          <t>5606 Premium Plus Ceiling Fan Blade - Ivory</t>
         </is>
       </c>
       <c r="G142" s="14" t="inlineStr">
@@ -10691,7 +10691,7 @@
         </is>
       </c>
       <c r="H142" s="16" t="n">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="I142" s="16" t="n">
         <v>0</v>
@@ -10703,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="16" t="n">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="M142" s="16" t="n">
         <v>0</v>
@@ -10715,10 +10715,10 @@
         <v>0</v>
       </c>
       <c r="P142" s="16" t="n">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="Q142" s="16" t="n">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="R142" s="16" t="n">
         <v>0</v>
@@ -10743,53 +10743,53 @@
       </c>
       <c r="D143" s="17" t="inlineStr">
         <is>
-          <t>1300100027</t>
+          <t>1300100133</t>
         </is>
       </c>
       <c r="E143" s="18" t="inlineStr">
         <is>
-          <t>SFG1010027</t>
+          <t>SFG1010136</t>
         </is>
       </c>
       <c r="F143" s="18" t="inlineStr">
         <is>
-          <t>Complete Armature 5.5 Circle 16mm</t>
+          <t>5607 Crown Ceiling Fan Blade - Ivory</t>
         </is>
       </c>
       <c r="G143" s="17" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H143" s="19" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="I143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J143" s="19" t="n">
-        <v>9338</v>
+        <v>0</v>
       </c>
       <c r="K143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L143" s="19" t="n">
-        <v>9338</v>
+        <v>149</v>
       </c>
       <c r="M143" s="19" t="n">
-        <v>9338</v>
+        <v>0</v>
       </c>
       <c r="N143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O143" s="19" t="n">
-        <v>9338</v>
+        <v>0</v>
       </c>
       <c r="P143" s="19" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="Q143" s="19" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="R143" s="19" t="n">
         <v>0</v>
@@ -10814,17 +10814,17 @@
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>1300100028</t>
+          <t>1300100027</t>
         </is>
       </c>
       <c r="E144" s="15" t="inlineStr">
         <is>
-          <t>SFG1010028</t>
+          <t>SFG1010027</t>
         </is>
       </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
-          <t>Complete Armature 6 Circle 16mm</t>
+          <t>Complete Armature 5.5 Circle 16mm</t>
         </is>
       </c>
       <c r="G144" s="14" t="inlineStr">
@@ -10839,22 +10839,22 @@
         <v>0</v>
       </c>
       <c r="J144" s="16" t="n">
-        <v>7415</v>
+        <v>9338</v>
       </c>
       <c r="K144" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L144" s="16" t="n">
-        <v>7415</v>
+        <v>9338</v>
       </c>
       <c r="M144" s="16" t="n">
-        <v>7415</v>
+        <v>9338</v>
       </c>
       <c r="N144" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O144" s="16" t="n">
-        <v>7415</v>
+        <v>9338</v>
       </c>
       <c r="P144" s="16" t="n">
         <v>0</v>
@@ -10885,17 +10885,17 @@
       </c>
       <c r="D145" s="17" t="inlineStr">
         <is>
-          <t>1300100030</t>
+          <t>1300100028</t>
         </is>
       </c>
       <c r="E145" s="18" t="inlineStr">
         <is>
-          <t>SFG1010030</t>
+          <t>SFG1010028</t>
         </is>
       </c>
       <c r="F145" s="18" t="inlineStr">
         <is>
-          <t>Complete Armature 7 Circle 15mm</t>
+          <t>Complete Armature 6 Circle 16mm</t>
         </is>
       </c>
       <c r="G145" s="17" t="inlineStr">
@@ -10904,34 +10904,34 @@
         </is>
       </c>
       <c r="H145" s="19" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="I145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J145" s="19" t="n">
-        <v>10297</v>
+        <v>7464</v>
       </c>
       <c r="K145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L145" s="19" t="n">
-        <v>10422</v>
+        <v>7464</v>
       </c>
       <c r="M145" s="19" t="n">
-        <v>10099</v>
+        <v>7464</v>
       </c>
       <c r="N145" s="19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O145" s="19" t="n">
-        <v>10124</v>
+        <v>7464</v>
       </c>
       <c r="P145" s="19" t="n">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="Q145" s="19" t="n">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="R145" s="19" t="n">
         <v>0</v>
@@ -10956,17 +10956,17 @@
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>1300100120</t>
+          <t>1300100030</t>
         </is>
       </c>
       <c r="E146" s="15" t="inlineStr">
         <is>
-          <t>SFG1010123</t>
+          <t>SFG1010030</t>
         </is>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
-          <t>Complete Armature 7 Circle 16mm -5607</t>
+          <t>Complete Armature 7 Circle 15mm</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
@@ -10975,34 +10975,34 @@
         </is>
       </c>
       <c r="H146" s="16" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="I146" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J146" s="16" t="n">
-        <v>1</v>
+        <v>13397</v>
       </c>
       <c r="K146" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L146" s="16" t="n">
-        <v>2</v>
+        <v>13522</v>
       </c>
       <c r="M146" s="16" t="n">
-        <v>0</v>
+        <v>10099</v>
       </c>
       <c r="N146" s="16" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="O146" s="16" t="n">
-        <v>2</v>
+        <v>10124</v>
       </c>
       <c r="P146" s="16" t="n">
-        <v>0</v>
+        <v>3398</v>
       </c>
       <c r="Q146" s="16" t="n">
-        <v>0</v>
+        <v>3398</v>
       </c>
       <c r="R146" s="16" t="n">
         <v>0</v>
@@ -11027,53 +11027,53 @@
       </c>
       <c r="D147" s="17" t="inlineStr">
         <is>
-          <t>1300100070</t>
+          <t>1300100120</t>
         </is>
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>SFG1010070</t>
+          <t>SFG1010123</t>
         </is>
       </c>
       <c r="F147" s="18" t="inlineStr">
         <is>
-          <t>Complete Canopy Big - 4801, 5601, 5603</t>
+          <t>Complete Armature 7 Circle 16mm -5607</t>
         </is>
       </c>
       <c r="G147" s="17" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H147" s="19" t="n">
-        <v>8647</v>
+        <v>1</v>
       </c>
       <c r="I147" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J147" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" s="19" t="n">
-        <v>21012</v>
+        <v>0</v>
       </c>
       <c r="L147" s="19" t="n">
-        <v>29659</v>
+        <v>2</v>
       </c>
       <c r="M147" s="19" t="n">
-        <v>21539</v>
+        <v>0</v>
       </c>
       <c r="N147" s="19" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="O147" s="19" t="n">
-        <v>21624</v>
+        <v>2</v>
       </c>
       <c r="P147" s="19" t="n">
-        <v>8035</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="19" t="n">
-        <v>8035</v>
+        <v>0</v>
       </c>
       <c r="R147" s="19" t="n">
         <v>0</v>
@@ -11098,26 +11098,26 @@
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>1300100105</t>
+          <t>1300100070</t>
         </is>
       </c>
       <c r="E148" s="15" t="inlineStr">
         <is>
-          <t>SFG1010110</t>
+          <t>SFG1010070</t>
         </is>
       </c>
       <c r="F148" s="15" t="inlineStr">
         <is>
-          <t>Complete Canopy Big-5601-White</t>
+          <t>Complete Canopy Big - 4801, 5601, 5603</t>
         </is>
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H148" s="16" t="n">
-        <v>545</v>
+        <v>8647</v>
       </c>
       <c r="I148" s="16" t="n">
         <v>0</v>
@@ -11126,25 +11126,25 @@
         <v>0</v>
       </c>
       <c r="K148" s="16" t="n">
-        <v>0</v>
+        <v>21912</v>
       </c>
       <c r="L148" s="16" t="n">
-        <v>545</v>
+        <v>30559</v>
       </c>
       <c r="M148" s="16" t="n">
-        <v>33</v>
+        <v>21588</v>
       </c>
       <c r="N148" s="16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O148" s="16" t="n">
-        <v>33</v>
+        <v>21673</v>
       </c>
       <c r="P148" s="16" t="n">
-        <v>512</v>
+        <v>8886</v>
       </c>
       <c r="Q148" s="16" t="n">
-        <v>512</v>
+        <v>8886</v>
       </c>
       <c r="R148" s="16" t="n">
         <v>0</v>
@@ -11169,17 +11169,17 @@
       </c>
       <c r="D149" s="17" t="inlineStr">
         <is>
-          <t>1300100069</t>
+          <t>1300100105</t>
         </is>
       </c>
       <c r="E149" s="18" t="inlineStr">
         <is>
-          <t>SFG1010069</t>
+          <t>SFG1010110</t>
         </is>
       </c>
       <c r="F149" s="18" t="inlineStr">
         <is>
-          <t>Complete Canopy Small-5602</t>
+          <t>Complete Canopy Big-5601-White</t>
         </is>
       </c>
       <c r="G149" s="17" t="inlineStr">
@@ -11188,7 +11188,7 @@
         </is>
       </c>
       <c r="H149" s="19" t="n">
-        <v>4680</v>
+        <v>545</v>
       </c>
       <c r="I149" s="19" t="n">
         <v>0</v>
@@ -11197,25 +11197,25 @@
         <v>0</v>
       </c>
       <c r="K149" s="19" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="L149" s="19" t="n">
-        <v>6480</v>
+        <v>545</v>
       </c>
       <c r="M149" s="19" t="n">
-        <v>5290</v>
+        <v>33</v>
       </c>
       <c r="N149" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O149" s="19" t="n">
-        <v>5290</v>
+        <v>33</v>
       </c>
       <c r="P149" s="19" t="n">
-        <v>1190</v>
+        <v>512</v>
       </c>
       <c r="Q149" s="19" t="n">
-        <v>1190</v>
+        <v>512</v>
       </c>
       <c r="R149" s="19" t="n">
         <v>0</v>
@@ -11240,17 +11240,17 @@
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>1300100065</t>
+          <t>1300100069</t>
         </is>
       </c>
       <c r="E150" s="15" t="inlineStr">
         <is>
-          <t>SFG1010065</t>
+          <t>SFG1010069</t>
         </is>
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>Complete Down Pipe 10 Inch -(5602,3601,2401)- Ivory</t>
+          <t>Complete Canopy Small-5602</t>
         </is>
       </c>
       <c r="G150" s="14" t="inlineStr">
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="H150" s="16" t="n">
-        <v>9083</v>
+        <v>4680</v>
       </c>
       <c r="I150" s="16" t="n">
         <v>0</v>
@@ -11268,25 +11268,25 @@
         <v>0</v>
       </c>
       <c r="K150" s="16" t="n">
-        <v>8034</v>
+        <v>1800</v>
       </c>
       <c r="L150" s="16" t="n">
-        <v>17117</v>
+        <v>6480</v>
       </c>
       <c r="M150" s="16" t="n">
-        <v>14628</v>
+        <v>5290</v>
       </c>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O150" s="16" t="n">
-        <v>14628</v>
+        <v>5290</v>
       </c>
       <c r="P150" s="16" t="n">
-        <v>2489</v>
+        <v>1190</v>
       </c>
       <c r="Q150" s="16" t="n">
-        <v>2489</v>
+        <v>1190</v>
       </c>
       <c r="R150" s="16" t="n">
         <v>0</v>
@@ -11311,17 +11311,17 @@
       </c>
       <c r="D151" s="17" t="inlineStr">
         <is>
-          <t>1300100064</t>
+          <t>1300100065</t>
         </is>
       </c>
       <c r="E151" s="18" t="inlineStr">
         <is>
-          <t>SFG1010064</t>
+          <t>SFG1010065</t>
         </is>
       </c>
       <c r="F151" s="18" t="inlineStr">
         <is>
-          <t>Complete Down Pipe 10 Inch- 4801, 5601, 5603 - Ivory</t>
+          <t>Complete Down Pipe 10 Inch -(5602,3601,2401)- Ivory</t>
         </is>
       </c>
       <c r="G151" s="17" t="inlineStr">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="H151" s="19" t="n">
-        <v>9955</v>
+        <v>9083</v>
       </c>
       <c r="I151" s="19" t="n">
         <v>0</v>
@@ -11339,25 +11339,25 @@
         <v>0</v>
       </c>
       <c r="K151" s="19" t="n">
-        <v>10465</v>
+        <v>9374</v>
       </c>
       <c r="L151" s="19" t="n">
-        <v>20420</v>
+        <v>18457</v>
       </c>
       <c r="M151" s="19" t="n">
-        <v>12191</v>
+        <v>14628</v>
       </c>
       <c r="N151" s="19" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O151" s="19" t="n">
-        <v>12276</v>
+        <v>14628</v>
       </c>
       <c r="P151" s="19" t="n">
-        <v>8144</v>
+        <v>3829</v>
       </c>
       <c r="Q151" s="19" t="n">
-        <v>8144</v>
+        <v>3829</v>
       </c>
       <c r="R151" s="19" t="n">
         <v>0</v>
@@ -11382,17 +11382,17 @@
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>1300100110</t>
+          <t>1300100064</t>
         </is>
       </c>
       <c r="E152" s="15" t="inlineStr">
         <is>
-          <t>SFG1010115</t>
+          <t>SFG1010064</t>
         </is>
       </c>
       <c r="F152" s="15" t="inlineStr">
         <is>
-          <t>Complete Down Pipe 10 Inch- 5601- White</t>
+          <t>Complete Down Pipe 10 Inch- 4801, 5601, 5603 - Ivory</t>
         </is>
       </c>
       <c r="G152" s="14" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="H152" s="16" t="n">
-        <v>230</v>
+        <v>9955</v>
       </c>
       <c r="I152" s="16" t="n">
         <v>0</v>
@@ -11410,25 +11410,25 @@
         <v>0</v>
       </c>
       <c r="K152" s="16" t="n">
-        <v>0</v>
+        <v>12035</v>
       </c>
       <c r="L152" s="16" t="n">
-        <v>230</v>
+        <v>21990</v>
       </c>
       <c r="M152" s="16" t="n">
-        <v>33</v>
+        <v>12240</v>
       </c>
       <c r="N152" s="16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O152" s="16" t="n">
-        <v>33</v>
+        <v>12325</v>
       </c>
       <c r="P152" s="16" t="n">
-        <v>197</v>
+        <v>9665</v>
       </c>
       <c r="Q152" s="16" t="n">
-        <v>197</v>
+        <v>9665</v>
       </c>
       <c r="R152" s="16" t="n">
         <v>0</v>
@@ -11453,17 +11453,17 @@
       </c>
       <c r="D153" s="17" t="inlineStr">
         <is>
-          <t>1300100039</t>
+          <t>1300100110</t>
         </is>
       </c>
       <c r="E153" s="18" t="inlineStr">
         <is>
-          <t>SFG1010039</t>
+          <t>SFG1010115</t>
         </is>
       </c>
       <c r="F153" s="18" t="inlineStr">
         <is>
-          <t>Complete Rotor 5.5 Circle 15.5mm</t>
+          <t>Complete Down Pipe 10 Inch- 5601- White</t>
         </is>
       </c>
       <c r="G153" s="17" t="inlineStr">
@@ -11472,34 +11472,34 @@
         </is>
       </c>
       <c r="H153" s="19" t="n">
-        <v>3986</v>
+        <v>230</v>
       </c>
       <c r="I153" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J153" s="19" t="n">
-        <v>5352</v>
+        <v>0</v>
       </c>
       <c r="K153" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L153" s="19" t="n">
-        <v>9338</v>
+        <v>230</v>
       </c>
       <c r="M153" s="19" t="n">
-        <v>9338</v>
+        <v>33</v>
       </c>
       <c r="N153" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O153" s="19" t="n">
-        <v>9338</v>
+        <v>33</v>
       </c>
       <c r="P153" s="19" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="Q153" s="19" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="R153" s="19" t="n">
         <v>0</v>
@@ -11524,17 +11524,17 @@
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>1300100040</t>
+          <t>1300100039</t>
         </is>
       </c>
       <c r="E154" s="15" t="inlineStr">
         <is>
-          <t>SFG1010040</t>
+          <t>SFG1010039</t>
         </is>
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>Complete Rotor 6 Circle 15.5mm</t>
+          <t>Complete Rotor 5.5 Circle 15.5mm</t>
         </is>
       </c>
       <c r="G154" s="14" t="inlineStr">
@@ -11543,34 +11543,34 @@
         </is>
       </c>
       <c r="H154" s="16" t="n">
-        <v>438</v>
+        <v>3986</v>
       </c>
       <c r="I154" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J154" s="16" t="n">
-        <v>7181</v>
+        <v>5352</v>
       </c>
       <c r="K154" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L154" s="16" t="n">
-        <v>7619</v>
+        <v>9338</v>
       </c>
       <c r="M154" s="16" t="n">
-        <v>7415</v>
+        <v>9338</v>
       </c>
       <c r="N154" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O154" s="16" t="n">
-        <v>7489</v>
+        <v>9338</v>
       </c>
       <c r="P154" s="16" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="Q154" s="16" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="R154" s="16" t="n">
         <v>0</v>
@@ -11595,17 +11595,17 @@
       </c>
       <c r="D155" s="17" t="inlineStr">
         <is>
-          <t>1300100042</t>
+          <t>1300100040</t>
         </is>
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
-          <t>SFG1010042</t>
+          <t>SFG1010040</t>
         </is>
       </c>
       <c r="F155" s="18" t="inlineStr">
         <is>
-          <t>Complete Rotor 7 Circle 14.5mm</t>
+          <t>Complete Rotor 6 Circle 15.5mm</t>
         </is>
       </c>
       <c r="G155" s="17" t="inlineStr">
@@ -11614,34 +11614,34 @@
         </is>
       </c>
       <c r="H155" s="19" t="n">
-        <v>1743</v>
+        <v>438</v>
       </c>
       <c r="I155" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J155" s="19" t="n">
-        <v>10070</v>
+        <v>7181</v>
       </c>
       <c r="K155" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L155" s="19" t="n">
-        <v>11813</v>
+        <v>7619</v>
       </c>
       <c r="M155" s="19" t="n">
-        <v>10099</v>
+        <v>7464</v>
       </c>
       <c r="N155" s="19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O155" s="19" t="n">
-        <v>10414</v>
+        <v>7538</v>
       </c>
       <c r="P155" s="19" t="n">
-        <v>1399</v>
+        <v>81</v>
       </c>
       <c r="Q155" s="19" t="n">
-        <v>1399</v>
+        <v>81</v>
       </c>
       <c r="R155" s="19" t="n">
         <v>0</v>
@@ -11666,17 +11666,17 @@
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>1300100123</t>
+          <t>1300100042</t>
         </is>
       </c>
       <c r="E156" s="15" t="inlineStr">
         <is>
-          <t>SFG1010126</t>
+          <t>SFG1010042</t>
         </is>
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>Complete Rotor 7 Circle 15.5mm</t>
+          <t>Complete Rotor 7 Circle 14.5mm</t>
         </is>
       </c>
       <c r="G156" s="14" t="inlineStr">
@@ -11685,34 +11685,34 @@
         </is>
       </c>
       <c r="H156" s="16" t="n">
-        <v>197</v>
+        <v>1743</v>
       </c>
       <c r="I156" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J156" s="16" t="n">
-        <v>200</v>
+        <v>13070</v>
       </c>
       <c r="K156" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L156" s="16" t="n">
-        <v>397</v>
+        <v>14813</v>
       </c>
       <c r="M156" s="16" t="n">
-        <v>0</v>
+        <v>10099</v>
       </c>
       <c r="N156" s="16" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="O156" s="16" t="n">
-        <v>2</v>
+        <v>10414</v>
       </c>
       <c r="P156" s="16" t="n">
-        <v>395</v>
+        <v>4399</v>
       </c>
       <c r="Q156" s="16" t="n">
-        <v>395</v>
+        <v>4399</v>
       </c>
       <c r="R156" s="16" t="n">
         <v>0</v>
@@ -11737,53 +11737,53 @@
       </c>
       <c r="D157" s="17" t="inlineStr">
         <is>
-          <t>1300100082</t>
+          <t>1300100123</t>
         </is>
       </c>
       <c r="E157" s="18" t="inlineStr">
         <is>
-          <t>SFG1010082</t>
+          <t>SFG1010126</t>
         </is>
       </c>
       <c r="F157" s="18" t="inlineStr">
         <is>
-          <t>Completed  Clamp with Accessories - 4801, 5601, 5603</t>
+          <t>Complete Rotor 7 Circle 15.5mm</t>
         </is>
       </c>
       <c r="G157" s="17" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H157" s="19" t="n">
-        <v>1808</v>
+        <v>197</v>
       </c>
       <c r="I157" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J157" s="19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K157" s="19" t="n">
-        <v>14060</v>
+        <v>0</v>
       </c>
       <c r="L157" s="19" t="n">
-        <v>15868</v>
+        <v>397</v>
       </c>
       <c r="M157" s="19" t="n">
-        <v>12224</v>
+        <v>0</v>
       </c>
       <c r="N157" s="19" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="O157" s="19" t="n">
-        <v>12309</v>
+        <v>2</v>
       </c>
       <c r="P157" s="19" t="n">
-        <v>3559</v>
+        <v>395</v>
       </c>
       <c r="Q157" s="19" t="n">
-        <v>3559</v>
+        <v>395</v>
       </c>
       <c r="R157" s="19" t="n">
         <v>0</v>
@@ -11808,17 +11808,17 @@
       </c>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>1300100139</t>
+          <t>1300100082</t>
         </is>
       </c>
       <c r="E158" s="15" t="inlineStr">
         <is>
-          <t>SFG1010142</t>
+          <t>SFG1010082</t>
         </is>
       </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
-          <t>Completed Clamp with Accessories - 5607</t>
+          <t>Completed  Clamp with Accessories - 4801, 5601, 5603</t>
         </is>
       </c>
       <c r="G158" s="14" t="inlineStr">
@@ -11827,7 +11827,7 @@
         </is>
       </c>
       <c r="H158" s="16" t="n">
-        <v>1</v>
+        <v>1808</v>
       </c>
       <c r="I158" s="16" t="n">
         <v>0</v>
@@ -11836,25 +11836,25 @@
         <v>0</v>
       </c>
       <c r="K158" s="16" t="n">
-        <v>396</v>
+        <v>14420</v>
       </c>
       <c r="L158" s="16" t="n">
-        <v>397</v>
+        <v>16228</v>
       </c>
       <c r="M158" s="16" t="n">
-        <v>0</v>
+        <v>12273</v>
       </c>
       <c r="N158" s="16" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="O158" s="16" t="n">
-        <v>2</v>
+        <v>12358</v>
       </c>
       <c r="P158" s="16" t="n">
-        <v>395</v>
+        <v>3870</v>
       </c>
       <c r="Q158" s="16" t="n">
-        <v>395</v>
+        <v>3870</v>
       </c>
       <c r="R158" s="16" t="n">
         <v>0</v>
@@ -11879,17 +11879,17 @@
       </c>
       <c r="D159" s="17" t="inlineStr">
         <is>
-          <t>1300100066</t>
+          <t>1300100139</t>
         </is>
       </c>
       <c r="E159" s="18" t="inlineStr">
         <is>
-          <t>SFG1010066</t>
+          <t>SFG1010142</t>
         </is>
       </c>
       <c r="F159" s="18" t="inlineStr">
         <is>
-          <t>Down Pipe Clamp - 4801, 5601, 5603</t>
+          <t>Completed Clamp with Accessories - 5607</t>
         </is>
       </c>
       <c r="G159" s="17" t="inlineStr">
@@ -11898,34 +11898,34 @@
         </is>
       </c>
       <c r="H159" s="19" t="n">
-        <v>593</v>
+        <v>1</v>
       </c>
       <c r="I159" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J159" s="19" t="n">
-        <v>17833</v>
+        <v>0</v>
       </c>
       <c r="K159" s="19" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="L159" s="19" t="n">
-        <v>18426</v>
+        <v>397</v>
       </c>
       <c r="M159" s="19" t="n">
-        <v>14456</v>
+        <v>0</v>
       </c>
       <c r="N159" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O159" s="19" t="n">
-        <v>14456</v>
+        <v>2</v>
       </c>
       <c r="P159" s="19" t="n">
-        <v>3970</v>
+        <v>395</v>
       </c>
       <c r="Q159" s="19" t="n">
-        <v>3970</v>
+        <v>395</v>
       </c>
       <c r="R159" s="19" t="n">
         <v>0</v>
@@ -11950,53 +11950,53 @@
       </c>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>1300100116</t>
+          <t>1300100066</t>
         </is>
       </c>
       <c r="E160" s="15" t="inlineStr">
         <is>
-          <t>SFG1010119</t>
+          <t>SFG1010066</t>
         </is>
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
-          <t>Fan Promotional Gang Regulator White (P512)</t>
+          <t>Down Pipe Clamp - 4801, 5601, 5603</t>
         </is>
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H160" s="16" t="n">
-        <v>244</v>
+        <v>593</v>
       </c>
       <c r="I160" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J160" s="16" t="n">
-        <v>0</v>
+        <v>17833</v>
       </c>
       <c r="K160" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L160" s="16" t="n">
-        <v>244</v>
+        <v>18426</v>
       </c>
       <c r="M160" s="16" t="n">
-        <v>0</v>
+        <v>14816</v>
       </c>
       <c r="N160" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O160" s="16" t="n">
-        <v>2</v>
+        <v>14816</v>
       </c>
       <c r="P160" s="16" t="n">
-        <v>242</v>
+        <v>3610</v>
       </c>
       <c r="Q160" s="16" t="n">
-        <v>242</v>
+        <v>3610</v>
       </c>
       <c r="R160" s="16" t="n">
         <v>0</v>
@@ -12021,17 +12021,17 @@
       </c>
       <c r="D161" s="17" t="inlineStr">
         <is>
-          <t>1300100081</t>
+          <t>1300100116</t>
         </is>
       </c>
       <c r="E161" s="18" t="inlineStr">
         <is>
-          <t>SFG1010081</t>
+          <t>SFG1010119</t>
         </is>
       </c>
       <c r="F161" s="18" t="inlineStr">
         <is>
-          <t>MEP Fan Regulator - 3601, 4801, 5601, 5603</t>
+          <t>Fan Promotional Gang Regulator White (P512)</t>
         </is>
       </c>
       <c r="G161" s="17" t="inlineStr">
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="H161" s="19" t="n">
-        <v>15468</v>
+        <v>244</v>
       </c>
       <c r="I161" s="19" t="n">
         <v>0</v>
@@ -12049,25 +12049,25 @@
         <v>0</v>
       </c>
       <c r="K161" s="19" t="n">
-        <v>30540</v>
+        <v>0</v>
       </c>
       <c r="L161" s="19" t="n">
-        <v>46008</v>
+        <v>244</v>
       </c>
       <c r="M161" s="19" t="n">
-        <v>19374</v>
+        <v>0</v>
       </c>
       <c r="N161" s="19" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="O161" s="19" t="n">
-        <v>19459</v>
+        <v>2</v>
       </c>
       <c r="P161" s="19" t="n">
-        <v>26549</v>
+        <v>242</v>
       </c>
       <c r="Q161" s="19" t="n">
-        <v>26549</v>
+        <v>242</v>
       </c>
       <c r="R161" s="19" t="n">
         <v>0</v>
@@ -12092,17 +12092,17 @@
       </c>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>1300100062</t>
+          <t>1300100081</t>
         </is>
       </c>
       <c r="E162" s="15" t="inlineStr">
         <is>
-          <t>SFG1010062</t>
+          <t>SFG1010081</t>
         </is>
       </c>
       <c r="F162" s="15" t="inlineStr">
         <is>
-          <t>Painted Down Pipe 10 Inch- 4801, 5601, 5603 - Ivory</t>
+          <t>MEP Fan Regulator - 3601, 4801, 5601, 5603</t>
         </is>
       </c>
       <c r="G162" s="14" t="inlineStr">
@@ -12111,34 +12111,34 @@
         </is>
       </c>
       <c r="H162" s="16" t="n">
-        <v>0</v>
+        <v>15468</v>
       </c>
       <c r="I162" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J162" s="16" t="n">
-        <v>10465</v>
+        <v>0</v>
       </c>
       <c r="K162" s="16" t="n">
-        <v>0</v>
+        <v>30540</v>
       </c>
       <c r="L162" s="16" t="n">
-        <v>10465</v>
+        <v>46008</v>
       </c>
       <c r="M162" s="16" t="n">
-        <v>10465</v>
+        <v>19423</v>
       </c>
       <c r="N162" s="16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O162" s="16" t="n">
-        <v>10465</v>
+        <v>19508</v>
       </c>
       <c r="P162" s="16" t="n">
-        <v>0</v>
+        <v>26500</v>
       </c>
       <c r="Q162" s="16" t="n">
-        <v>0</v>
+        <v>26500</v>
       </c>
       <c r="R162" s="16" t="n">
         <v>0</v>
@@ -12163,17 +12163,17 @@
       </c>
       <c r="D163" s="17" t="inlineStr">
         <is>
-          <t>1300100063</t>
+          <t>1300100062</t>
         </is>
       </c>
       <c r="E163" s="18" t="inlineStr">
         <is>
-          <t>SFG1010063</t>
+          <t>SFG1010062</t>
         </is>
       </c>
       <c r="F163" s="18" t="inlineStr">
         <is>
-          <t>Painted Down Pipe 10 Inch-5602,3601,2401 - Ivory</t>
+          <t>Painted Down Pipe 10 Inch- 4801, 5601, 5603 - Ivory</t>
         </is>
       </c>
       <c r="G163" s="17" t="inlineStr">
@@ -12188,22 +12188,22 @@
         <v>0</v>
       </c>
       <c r="J163" s="19" t="n">
-        <v>8034</v>
+        <v>12035</v>
       </c>
       <c r="K163" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L163" s="19" t="n">
-        <v>8034</v>
+        <v>12035</v>
       </c>
       <c r="M163" s="19" t="n">
-        <v>8034</v>
+        <v>12035</v>
       </c>
       <c r="N163" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O163" s="19" t="n">
-        <v>8034</v>
+        <v>12035</v>
       </c>
       <c r="P163" s="19" t="n">
         <v>0</v>
@@ -12234,47 +12234,47 @@
       </c>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>1300100055</t>
+          <t>1300100063</t>
         </is>
       </c>
       <c r="E164" s="15" t="inlineStr">
         <is>
-          <t>SFG1010055</t>
+          <t>SFG1010063</t>
         </is>
       </c>
       <c r="F164" s="15" t="inlineStr">
         <is>
-          <t>Painting Blade 2401-Ivory</t>
+          <t>Painted Down Pipe 10 Inch-5602,3601,2401 - Ivory</t>
         </is>
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H164" s="16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I164" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J164" s="16" t="n">
-        <v>0</v>
+        <v>9374</v>
       </c>
       <c r="K164" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L164" s="16" t="n">
-        <v>21</v>
+        <v>9374</v>
       </c>
       <c r="M164" s="16" t="n">
-        <v>0</v>
+        <v>9374</v>
       </c>
       <c r="N164" s="16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O164" s="16" t="n">
-        <v>21</v>
+        <v>9374</v>
       </c>
       <c r="P164" s="16" t="n">
         <v>0</v>
@@ -12305,17 +12305,17 @@
       </c>
       <c r="D165" s="17" t="inlineStr">
         <is>
-          <t>1300100056</t>
+          <t>1300100055</t>
         </is>
       </c>
       <c r="E165" s="18" t="inlineStr">
         <is>
-          <t>SFG1010056</t>
+          <t>SFG1010055</t>
         </is>
       </c>
       <c r="F165" s="18" t="inlineStr">
         <is>
-          <t>Painting Blade 3601-Ivory</t>
+          <t>Painting Blade 2401-Ivory</t>
         </is>
       </c>
       <c r="G165" s="17" t="inlineStr">
@@ -12324,28 +12324,28 @@
         </is>
       </c>
       <c r="H165" s="19" t="n">
-        <v>452</v>
+        <v>21</v>
       </c>
       <c r="I165" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J165" s="19" t="n">
-        <v>7675</v>
+        <v>0</v>
       </c>
       <c r="K165" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L165" s="19" t="n">
-        <v>8127</v>
+        <v>21</v>
       </c>
       <c r="M165" s="19" t="n">
-        <v>8107</v>
+        <v>0</v>
       </c>
       <c r="N165" s="19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O165" s="19" t="n">
-        <v>8127</v>
+        <v>21</v>
       </c>
       <c r="P165" s="19" t="n">
         <v>0</v>
@@ -12376,17 +12376,17 @@
       </c>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>1300100057</t>
+          <t>1300100056</t>
         </is>
       </c>
       <c r="E166" s="15" t="inlineStr">
         <is>
-          <t>SFG1010057</t>
+          <t>SFG1010056</t>
         </is>
       </c>
       <c r="F166" s="15" t="inlineStr">
         <is>
-          <t>Painting Blade 4801-Ivory</t>
+          <t>Painting Blade 3601-Ivory</t>
         </is>
       </c>
       <c r="G166" s="14" t="inlineStr">
@@ -12395,34 +12395,34 @@
         </is>
       </c>
       <c r="H166" s="16" t="n">
-        <v>21</v>
+        <v>452</v>
       </c>
       <c r="I166" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J166" s="16" t="n">
-        <v>3665</v>
+        <v>7675</v>
       </c>
       <c r="K166" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L166" s="16" t="n">
-        <v>3686</v>
+        <v>8127</v>
       </c>
       <c r="M166" s="16" t="n">
-        <v>2070</v>
+        <v>8107</v>
       </c>
       <c r="N166" s="16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O166" s="16" t="n">
-        <v>2070</v>
+        <v>8127</v>
       </c>
       <c r="P166" s="16" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="Q166" s="16" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="R166" s="16" t="n">
         <v>0</v>
@@ -12447,17 +12447,17 @@
       </c>
       <c r="D167" s="17" t="inlineStr">
         <is>
-          <t>1300100058</t>
+          <t>1300100057</t>
         </is>
       </c>
       <c r="E167" s="18" t="inlineStr">
         <is>
-          <t>SFG1010058</t>
+          <t>SFG1010057</t>
         </is>
       </c>
       <c r="F167" s="18" t="inlineStr">
         <is>
-          <t>Painting Blade 5601-Ivory</t>
+          <t>Painting Blade 4801-Ivory</t>
         </is>
       </c>
       <c r="G167" s="17" t="inlineStr">
@@ -12466,34 +12466,34 @@
         </is>
       </c>
       <c r="H167" s="19" t="n">
-        <v>607</v>
+        <v>21</v>
       </c>
       <c r="I167" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J167" s="19" t="n">
-        <v>3554</v>
+        <v>4808</v>
       </c>
       <c r="K167" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L167" s="19" t="n">
-        <v>4161</v>
+        <v>4829</v>
       </c>
       <c r="M167" s="19" t="n">
-        <v>4150</v>
+        <v>3730</v>
       </c>
       <c r="N167" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O167" s="19" t="n">
-        <v>4150</v>
+        <v>3730</v>
       </c>
       <c r="P167" s="19" t="n">
-        <v>11</v>
+        <v>1099</v>
       </c>
       <c r="Q167" s="19" t="n">
-        <v>11</v>
+        <v>1099</v>
       </c>
       <c r="R167" s="19" t="n">
         <v>0</v>
@@ -12518,17 +12518,17 @@
       </c>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>1300100102</t>
+          <t>1300100058</t>
         </is>
       </c>
       <c r="E168" s="15" t="inlineStr">
         <is>
-          <t>SFG1010107</t>
+          <t>SFG1010058</t>
         </is>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>Painting Blade 5601-White</t>
+          <t>Painting Blade 5601-Ivory</t>
         </is>
       </c>
       <c r="G168" s="14" t="inlineStr">
@@ -12537,34 +12537,34 @@
         </is>
       </c>
       <c r="H168" s="16" t="n">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="I168" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J168" s="16" t="n">
-        <v>100</v>
+        <v>5409</v>
       </c>
       <c r="K168" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L168" s="16" t="n">
-        <v>100</v>
+        <v>6016</v>
       </c>
       <c r="M168" s="16" t="n">
-        <v>100</v>
+        <v>5520</v>
       </c>
       <c r="N168" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O168" s="16" t="n">
-        <v>100</v>
+        <v>5520</v>
       </c>
       <c r="P168" s="16" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="Q168" s="16" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="R168" s="16" t="n">
         <v>0</v>
@@ -12589,17 +12589,17 @@
       </c>
       <c r="D169" s="17" t="inlineStr">
         <is>
-          <t>1300100059</t>
+          <t>1300100102</t>
         </is>
       </c>
       <c r="E169" s="18" t="inlineStr">
         <is>
-          <t>SFG1010059</t>
+          <t>SFG1010107</t>
         </is>
       </c>
       <c r="F169" s="18" t="inlineStr">
         <is>
-          <t>Painting Blade 5602-Ivory</t>
+          <t>Painting Blade 5601-White</t>
         </is>
       </c>
       <c r="G169" s="17" t="inlineStr">
@@ -12614,28 +12614,28 @@
         <v>0</v>
       </c>
       <c r="J169" s="19" t="n">
-        <v>4923</v>
+        <v>100</v>
       </c>
       <c r="K169" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L169" s="19" t="n">
-        <v>4923</v>
+        <v>100</v>
       </c>
       <c r="M169" s="19" t="n">
-        <v>4414</v>
+        <v>100</v>
       </c>
       <c r="N169" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O169" s="19" t="n">
-        <v>4414</v>
+        <v>100</v>
       </c>
       <c r="P169" s="19" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="Q169" s="19" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="R169" s="19" t="n">
         <v>0</v>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>1300100090</t>
+          <t>1300100059</t>
         </is>
       </c>
       <c r="E170" s="15" t="inlineStr">
         <is>
-          <t>SFG1010095</t>
+          <t>SFG1010059</t>
         </is>
       </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
-          <t>Painting Blade 5603-Ivory</t>
+          <t>Painting Blade 5602-Ivory</t>
         </is>
       </c>
       <c r="G170" s="14" t="inlineStr">
@@ -12679,34 +12679,34 @@
         </is>
       </c>
       <c r="H170" s="16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I170" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J170" s="16" t="n">
-        <v>1890</v>
+        <v>4923</v>
       </c>
       <c r="K170" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L170" s="16" t="n">
-        <v>1898</v>
+        <v>4923</v>
       </c>
       <c r="M170" s="16" t="n">
-        <v>1533</v>
+        <v>4923</v>
       </c>
       <c r="N170" s="16" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="O170" s="16" t="n">
-        <v>1883</v>
+        <v>4923</v>
       </c>
       <c r="P170" s="16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q170" s="16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R170" s="16" t="n">
         <v>0</v>
@@ -12731,17 +12731,17 @@
       </c>
       <c r="D171" s="17" t="inlineStr">
         <is>
-          <t>1300100127</t>
+          <t>1300100090</t>
         </is>
       </c>
       <c r="E171" s="18" t="inlineStr">
         <is>
-          <t>SFG1010130</t>
+          <t>SFG1010095</t>
         </is>
       </c>
       <c r="F171" s="18" t="inlineStr">
         <is>
-          <t>Painting Blade 5607 - Ivory</t>
+          <t>Painting Blade 5603-Ivory</t>
         </is>
       </c>
       <c r="G171" s="17" t="inlineStr">
@@ -12750,34 +12750,34 @@
         </is>
       </c>
       <c r="H171" s="19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I171" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J171" s="19" t="n">
-        <v>0</v>
+        <v>1890</v>
       </c>
       <c r="K171" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L171" s="19" t="n">
-        <v>5</v>
+        <v>1898</v>
       </c>
       <c r="M171" s="19" t="n">
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="N171" s="19" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="O171" s="19" t="n">
-        <v>0</v>
+        <v>1883</v>
       </c>
       <c r="P171" s="19" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q171" s="19" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R171" s="19" t="n">
         <v>0</v>
@@ -12802,53 +12802,53 @@
       </c>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>1300100131</t>
+          <t>1300100127</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr">
         <is>
-          <t>SFG1010134</t>
+          <t>SFG1010130</t>
         </is>
       </c>
       <c r="F172" s="15" t="inlineStr">
         <is>
-          <t>Painting Bottom Cover 5607 - Ivory</t>
+          <t>Painting Blade 5607 - Ivory</t>
         </is>
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H172" s="16" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="I172" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J172" s="16" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="K172" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L172" s="16" t="n">
-        <v>395</v>
+        <v>5</v>
       </c>
       <c r="M172" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N172" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O172" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P172" s="16" t="n">
-        <v>393</v>
+        <v>5</v>
       </c>
       <c r="Q172" s="16" t="n">
-        <v>393</v>
+        <v>5</v>
       </c>
       <c r="R172" s="16" t="n">
         <v>0</v>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="D173" s="17" t="inlineStr">
         <is>
-          <t>1300100014</t>
+          <t>1300100131</t>
         </is>
       </c>
       <c r="E173" s="18" t="inlineStr">
         <is>
-          <t>SFG1010014</t>
+          <t>SFG1010134</t>
         </is>
       </c>
       <c r="F173" s="18" t="inlineStr">
         <is>
-          <t>Painting Bottom Cover-2401 (184mm) - Ivory</t>
+          <t>Painting Bottom Cover 5607 - Ivory</t>
         </is>
       </c>
       <c r="G173" s="17" t="inlineStr">
@@ -12892,34 +12892,34 @@
         </is>
       </c>
       <c r="H173" s="19" t="n">
-        <v>2155</v>
+        <v>41</v>
       </c>
       <c r="I173" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J173" s="19" t="n">
+        <v>404</v>
+      </c>
+      <c r="K173" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" s="19" t="n">
+        <v>445</v>
+      </c>
+      <c r="M173" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O173" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="K173" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="19" t="n">
-        <v>2189</v>
-      </c>
-      <c r="M173" s="19" t="n">
-        <v>2188</v>
-      </c>
-      <c r="N173" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O173" s="19" t="n">
-        <v>2189</v>
-      </c>
       <c r="P173" s="19" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="Q173" s="19" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="R173" s="19" t="n">
         <v>0</v>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="D174" s="14" t="inlineStr">
         <is>
-          <t>1300100015</t>
+          <t>1300100014</t>
         </is>
       </c>
       <c r="E174" s="15" t="inlineStr">
         <is>
-          <t>SFG1010015</t>
+          <t>SFG1010014</t>
         </is>
       </c>
       <c r="F174" s="15" t="inlineStr">
         <is>
-          <t>Painting Bottom Cover-3601 (184mm) - Ivory</t>
+          <t>Painting Bottom Cover-2401 (184mm) - Ivory</t>
         </is>
       </c>
       <c r="G174" s="14" t="inlineStr">
@@ -12963,34 +12963,34 @@
         </is>
       </c>
       <c r="H174" s="16" t="n">
-        <v>1850</v>
+        <v>2155</v>
       </c>
       <c r="I174" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J174" s="16" t="n">
-        <v>5700</v>
+        <v>34</v>
       </c>
       <c r="K174" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L174" s="16" t="n">
-        <v>7550</v>
+        <v>2189</v>
       </c>
       <c r="M174" s="16" t="n">
-        <v>7150</v>
+        <v>2188</v>
       </c>
       <c r="N174" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O174" s="16" t="n">
-        <v>7150</v>
+        <v>2189</v>
       </c>
       <c r="P174" s="16" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Q174" s="16" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R174" s="16" t="n">
         <v>0</v>
@@ -13015,17 +13015,17 @@
       </c>
       <c r="D175" s="17" t="inlineStr">
         <is>
-          <t>1300100016</t>
+          <t>1300100015</t>
         </is>
       </c>
       <c r="E175" s="18" t="inlineStr">
         <is>
-          <t>SFG1010016</t>
+          <t>SFG1010015</t>
         </is>
       </c>
       <c r="F175" s="18" t="inlineStr">
         <is>
-          <t>Painting Bottom Cover-4801 (220mm) - Ivory</t>
+          <t>Painting Bottom Cover-3601 (184mm) - Ivory</t>
         </is>
       </c>
       <c r="G175" s="17" t="inlineStr">
@@ -13034,34 +13034,34 @@
         </is>
       </c>
       <c r="H175" s="19" t="n">
-        <v>532</v>
+        <v>1850</v>
       </c>
       <c r="I175" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J175" s="19" t="n">
-        <v>1781</v>
+        <v>5700</v>
       </c>
       <c r="K175" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L175" s="19" t="n">
-        <v>2313</v>
+        <v>7550</v>
       </c>
       <c r="M175" s="19" t="n">
-        <v>2125</v>
+        <v>7150</v>
       </c>
       <c r="N175" s="19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O175" s="19" t="n">
-        <v>2296</v>
+        <v>7186</v>
       </c>
       <c r="P175" s="19" t="n">
-        <v>17</v>
+        <v>364</v>
       </c>
       <c r="Q175" s="19" t="n">
-        <v>17</v>
+        <v>364</v>
       </c>
       <c r="R175" s="19" t="n">
         <v>0</v>
@@ -13086,17 +13086,17 @@
       </c>
       <c r="D176" s="14" t="inlineStr">
         <is>
-          <t>1300100017</t>
+          <t>1300100016</t>
         </is>
       </c>
       <c r="E176" s="15" t="inlineStr">
         <is>
-          <t>SFG1010017</t>
+          <t>SFG1010016</t>
         </is>
       </c>
       <c r="F176" s="15" t="inlineStr">
         <is>
-          <t>Painting Bottom Cover-5601 (232mm) - Ivory</t>
+          <t>Painting Bottom Cover-4801 (220mm) - Ivory</t>
         </is>
       </c>
       <c r="G176" s="14" t="inlineStr">
@@ -13105,34 +13105,34 @@
         </is>
       </c>
       <c r="H176" s="16" t="n">
-        <v>605</v>
+        <v>532</v>
       </c>
       <c r="I176" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J176" s="16" t="n">
-        <v>10996</v>
+        <v>1830</v>
       </c>
       <c r="K176" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L176" s="16" t="n">
-        <v>11601</v>
+        <v>2362</v>
       </c>
       <c r="M176" s="16" t="n">
-        <v>9415</v>
+        <v>2174</v>
       </c>
       <c r="N176" s="16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O176" s="16" t="n">
-        <v>9447</v>
+        <v>2362</v>
       </c>
       <c r="P176" s="16" t="n">
-        <v>2154</v>
+        <v>0</v>
       </c>
       <c r="Q176" s="16" t="n">
-        <v>2154</v>
+        <v>0</v>
       </c>
       <c r="R176" s="16" t="n">
         <v>0</v>
@@ -13157,17 +13157,17 @@
       </c>
       <c r="D177" s="17" t="inlineStr">
         <is>
-          <t>1300100101</t>
+          <t>1300100017</t>
         </is>
       </c>
       <c r="E177" s="18" t="inlineStr">
         <is>
-          <t>SFG1010106</t>
+          <t>SFG1010017</t>
         </is>
       </c>
       <c r="F177" s="18" t="inlineStr">
         <is>
-          <t>Painting Bottom Cover-5601 (232mm) - White</t>
+          <t>Painting Bottom Cover-5601 (232mm) - Ivory</t>
         </is>
       </c>
       <c r="G177" s="17" t="inlineStr">
@@ -13176,34 +13176,34 @@
         </is>
       </c>
       <c r="H177" s="19" t="n">
-        <v>125</v>
+        <v>605</v>
       </c>
       <c r="I177" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J177" s="19" t="n">
-        <v>0</v>
+        <v>12596</v>
       </c>
       <c r="K177" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L177" s="19" t="n">
-        <v>125</v>
+        <v>13201</v>
       </c>
       <c r="M177" s="19" t="n">
-        <v>33</v>
+        <v>9415</v>
       </c>
       <c r="N177" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O177" s="19" t="n">
-        <v>33</v>
+        <v>9524</v>
       </c>
       <c r="P177" s="19" t="n">
-        <v>92</v>
+        <v>3677</v>
       </c>
       <c r="Q177" s="19" t="n">
-        <v>92</v>
+        <v>3677</v>
       </c>
       <c r="R177" s="19" t="n">
         <v>0</v>
@@ -13228,17 +13228,17 @@
       </c>
       <c r="D178" s="14" t="inlineStr">
         <is>
-          <t>1300100018</t>
+          <t>1300100101</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr">
         <is>
-          <t>SFG1010018</t>
+          <t>SFG1010106</t>
         </is>
       </c>
       <c r="F178" s="15" t="inlineStr">
         <is>
-          <t>Painting Bottom Cover-5602 (217mm) - Ivory</t>
+          <t>Painting Bottom Cover-5601 (232mm) - White</t>
         </is>
       </c>
       <c r="G178" s="14" t="inlineStr">
@@ -13247,34 +13247,34 @@
         </is>
       </c>
       <c r="H178" s="16" t="n">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="I178" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J178" s="16" t="n">
-        <v>5307</v>
+        <v>0</v>
       </c>
       <c r="K178" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L178" s="16" t="n">
-        <v>5363</v>
+        <v>125</v>
       </c>
       <c r="M178" s="16" t="n">
-        <v>5290</v>
+        <v>33</v>
       </c>
       <c r="N178" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O178" s="16" t="n">
-        <v>5310</v>
+        <v>33</v>
       </c>
       <c r="P178" s="16" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="Q178" s="16" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="R178" s="16" t="n">
         <v>0</v>
@@ -13299,17 +13299,17 @@
       </c>
       <c r="D179" s="17" t="inlineStr">
         <is>
-          <t>1300100087</t>
+          <t>1300100018</t>
         </is>
       </c>
       <c r="E179" s="18" t="inlineStr">
         <is>
-          <t>SFG1010092</t>
+          <t>SFG1010018</t>
         </is>
       </c>
       <c r="F179" s="18" t="inlineStr">
         <is>
-          <t>Painting Bottom Cover-5603 (232mm) - Ivory</t>
+          <t>Painting Bottom Cover-5602 (217mm) - Ivory</t>
         </is>
       </c>
       <c r="G179" s="17" t="inlineStr">
@@ -13318,28 +13318,28 @@
         </is>
       </c>
       <c r="H179" s="19" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="I179" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J179" s="19" t="n">
-        <v>785</v>
+        <v>5307</v>
       </c>
       <c r="K179" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L179" s="19" t="n">
-        <v>801</v>
+        <v>5363</v>
       </c>
       <c r="M179" s="19" t="n">
-        <v>651</v>
+        <v>5290</v>
       </c>
       <c r="N179" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O179" s="19" t="n">
-        <v>801</v>
+        <v>5363</v>
       </c>
       <c r="P179" s="19" t="n">
         <v>0</v>
@@ -13370,47 +13370,47 @@
       </c>
       <c r="D180" s="14" t="inlineStr">
         <is>
-          <t>1300100098</t>
+          <t>1300100087</t>
         </is>
       </c>
       <c r="E180" s="15" t="inlineStr">
         <is>
-          <t>SFG1010103</t>
+          <t>SFG1010092</t>
         </is>
       </c>
       <c r="F180" s="15" t="inlineStr">
         <is>
-          <t>Painting Down pipe 1 Inch</t>
+          <t>Painting Bottom Cover-5603 (232mm) - Ivory</t>
         </is>
       </c>
       <c r="G180" s="14" t="inlineStr">
         <is>
-          <t>Inch</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="H180" s="16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I180" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J180" s="16" t="n">
-        <v>6000</v>
+        <v>785</v>
       </c>
       <c r="K180" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L180" s="16" t="n">
-        <v>6000</v>
+        <v>801</v>
       </c>
       <c r="M180" s="16" t="n">
-        <v>6000</v>
+        <v>651</v>
       </c>
       <c r="N180" s="16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O180" s="16" t="n">
-        <v>6000</v>
+        <v>801</v>
       </c>
       <c r="P180" s="16" t="n">
         <v>0</v>
@@ -13441,53 +13441,53 @@
       </c>
       <c r="D181" s="17" t="inlineStr">
         <is>
-          <t>1300100130</t>
+          <t>1300100098</t>
         </is>
       </c>
       <c r="E181" s="18" t="inlineStr">
         <is>
-          <t>SFG1010133</t>
+          <t>SFG1010103</t>
         </is>
       </c>
       <c r="F181" s="18" t="inlineStr">
         <is>
-          <t>Painting Top Cover 5607 - Ivory</t>
+          <t>Painting Down pipe 1 Inch</t>
         </is>
       </c>
       <c r="G181" s="17" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Inch</t>
         </is>
       </c>
       <c r="H181" s="19" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I181" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J181" s="19" t="n">
-        <v>305</v>
+        <v>6000</v>
       </c>
       <c r="K181" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L181" s="19" t="n">
-        <v>455</v>
+        <v>6000</v>
       </c>
       <c r="M181" s="19" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="N181" s="19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O181" s="19" t="n">
-        <v>2</v>
+        <v>6000</v>
       </c>
       <c r="P181" s="19" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="Q181" s="19" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="R181" s="19" t="n">
         <v>0</v>
@@ -13512,17 +13512,17 @@
       </c>
       <c r="D182" s="14" t="inlineStr">
         <is>
-          <t>1300100005</t>
+          <t>1300100130</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr">
         <is>
-          <t>SFG1010005</t>
+          <t>SFG1010133</t>
         </is>
       </c>
       <c r="F182" s="15" t="inlineStr">
         <is>
-          <t>Painting Top Cover-2401 (184mm)-  Ivory</t>
+          <t>Painting Top Cover 5607 - Ivory</t>
         </is>
       </c>
       <c r="G182" s="14" t="inlineStr">
@@ -13531,34 +13531,34 @@
         </is>
       </c>
       <c r="H182" s="16" t="n">
-        <v>2156</v>
+        <v>150</v>
       </c>
       <c r="I182" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J182" s="16" t="n">
-        <v>32</v>
+        <v>355</v>
       </c>
       <c r="K182" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L182" s="16" t="n">
-        <v>2188</v>
+        <v>505</v>
       </c>
       <c r="M182" s="16" t="n">
-        <v>2188</v>
+        <v>0</v>
       </c>
       <c r="N182" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O182" s="16" t="n">
-        <v>2188</v>
+        <v>33</v>
       </c>
       <c r="P182" s="16" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="Q182" s="16" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="R182" s="16" t="n">
         <v>0</v>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D183" s="17" t="inlineStr">
         <is>
-          <t>1300100006</t>
+          <t>1300100005</t>
         </is>
       </c>
       <c r="E183" s="18" t="inlineStr">
         <is>
-          <t>SFG1010006</t>
+          <t>SFG1010005</t>
         </is>
       </c>
       <c r="F183" s="18" t="inlineStr">
         <is>
-          <t>Painting Top Cover-3601 (184mm) - Ivory</t>
+          <t>Painting Top Cover-2401 (184mm)-  Ivory</t>
         </is>
       </c>
       <c r="G183" s="17" t="inlineStr">
@@ -13602,34 +13602,34 @@
         </is>
       </c>
       <c r="H183" s="19" t="n">
-        <v>1976</v>
+        <v>2156</v>
       </c>
       <c r="I183" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J183" s="19" t="n">
-        <v>5582</v>
+        <v>32</v>
       </c>
       <c r="K183" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L183" s="19" t="n">
-        <v>7558</v>
+        <v>2188</v>
       </c>
       <c r="M183" s="19" t="n">
-        <v>7150</v>
+        <v>2188</v>
       </c>
       <c r="N183" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O183" s="19" t="n">
-        <v>7150</v>
+        <v>2188</v>
       </c>
       <c r="P183" s="19" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="Q183" s="19" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="R183" s="19" t="n">
         <v>0</v>
@@ -13654,17 +13654,17 @@
       </c>
       <c r="D184" s="14" t="inlineStr">
         <is>
-          <t>1300100007</t>
+          <t>1300100006</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr">
         <is>
-          <t>SFG1010007</t>
+          <t>SFG1010006</t>
         </is>
       </c>
       <c r="F184" s="15" t="inlineStr">
         <is>
-          <t>Painting Top Cover-4801 (220mm) - Ivory</t>
+          <t>Painting Top Cover-3601 (184mm) - Ivory</t>
         </is>
       </c>
       <c r="G184" s="14" t="inlineStr">
@@ -13673,34 +13673,34 @@
         </is>
       </c>
       <c r="H184" s="16" t="n">
-        <v>528</v>
+        <v>1976</v>
       </c>
       <c r="I184" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J184" s="16" t="n">
-        <v>1763</v>
+        <v>5582</v>
       </c>
       <c r="K184" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L184" s="16" t="n">
-        <v>2291</v>
+        <v>7558</v>
       </c>
       <c r="M184" s="16" t="n">
-        <v>2125</v>
+        <v>7150</v>
       </c>
       <c r="N184" s="16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O184" s="16" t="n">
-        <v>2279</v>
+        <v>7285</v>
       </c>
       <c r="P184" s="16" t="n">
-        <v>12</v>
+        <v>273</v>
       </c>
       <c r="Q184" s="16" t="n">
-        <v>12</v>
+        <v>273</v>
       </c>
       <c r="R184" s="16" t="n">
         <v>0</v>
@@ -13725,17 +13725,17 @@
       </c>
       <c r="D185" s="17" t="inlineStr">
         <is>
-          <t>1300100008</t>
+          <t>1300100007</t>
         </is>
       </c>
       <c r="E185" s="18" t="inlineStr">
         <is>
-          <t>SFG1010008</t>
+          <t>SFG1010007</t>
         </is>
       </c>
       <c r="F185" s="18" t="inlineStr">
         <is>
-          <t>Painting Top Cover-5601 (232mm) - Ivory</t>
+          <t>Painting Top Cover-4801 (220mm) - Ivory</t>
         </is>
       </c>
       <c r="G185" s="17" t="inlineStr">
@@ -13744,34 +13744,34 @@
         </is>
       </c>
       <c r="H185" s="19" t="n">
-        <v>1014</v>
+        <v>528</v>
       </c>
       <c r="I185" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J185" s="19" t="n">
-        <v>11199</v>
+        <v>1812</v>
       </c>
       <c r="K185" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L185" s="19" t="n">
-        <v>12213</v>
+        <v>2340</v>
       </c>
       <c r="M185" s="19" t="n">
-        <v>9415</v>
+        <v>2174</v>
       </c>
       <c r="N185" s="19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O185" s="19" t="n">
-        <v>9468</v>
+        <v>2340</v>
       </c>
       <c r="P185" s="19" t="n">
-        <v>2745</v>
+        <v>0</v>
       </c>
       <c r="Q185" s="19" t="n">
-        <v>2745</v>
+        <v>0</v>
       </c>
       <c r="R185" s="19" t="n">
         <v>0</v>
@@ -13796,17 +13796,17 @@
       </c>
       <c r="D186" s="14" t="inlineStr">
         <is>
-          <t>1300100100</t>
+          <t>1300100008</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr">
         <is>
-          <t>SFG1010105</t>
+          <t>SFG1010008</t>
         </is>
       </c>
       <c r="F186" s="15" t="inlineStr">
         <is>
-          <t>Painting Top Cover-5601 (232mm) - White</t>
+          <t>Painting Top Cover-5601 (232mm) - Ivory</t>
         </is>
       </c>
       <c r="G186" s="14" t="inlineStr">
@@ -13815,34 +13815,34 @@
         </is>
       </c>
       <c r="H186" s="16" t="n">
-        <v>125</v>
+        <v>1014</v>
       </c>
       <c r="I186" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J186" s="16" t="n">
-        <v>0</v>
+        <v>12199</v>
       </c>
       <c r="K186" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L186" s="16" t="n">
-        <v>125</v>
+        <v>13213</v>
       </c>
       <c r="M186" s="16" t="n">
-        <v>33</v>
+        <v>9415</v>
       </c>
       <c r="N186" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O186" s="16" t="n">
-        <v>33</v>
+        <v>9517</v>
       </c>
       <c r="P186" s="16" t="n">
-        <v>92</v>
+        <v>3696</v>
       </c>
       <c r="Q186" s="16" t="n">
-        <v>92</v>
+        <v>3696</v>
       </c>
       <c r="R186" s="16" t="n">
         <v>0</v>
@@ -13867,17 +13867,17 @@
       </c>
       <c r="D187" s="17" t="inlineStr">
         <is>
-          <t>1300100009</t>
+          <t>1300100100</t>
         </is>
       </c>
       <c r="E187" s="18" t="inlineStr">
         <is>
-          <t>SFG1010009</t>
+          <t>SFG1010105</t>
         </is>
       </c>
       <c r="F187" s="18" t="inlineStr">
         <is>
-          <t>Painting Top Cover-5602 (217mm) - Ivory</t>
+          <t>Painting Top Cover-5601 (232mm) - White</t>
         </is>
       </c>
       <c r="G187" s="17" t="inlineStr">
@@ -13886,34 +13886,34 @@
         </is>
       </c>
       <c r="H187" s="19" t="n">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="I187" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J187" s="19" t="n">
-        <v>5587</v>
+        <v>0</v>
       </c>
       <c r="K187" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L187" s="19" t="n">
-        <v>5600</v>
+        <v>125</v>
       </c>
       <c r="M187" s="19" t="n">
-        <v>5290</v>
+        <v>33</v>
       </c>
       <c r="N187" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O187" s="19" t="n">
-        <v>5316</v>
+        <v>33</v>
       </c>
       <c r="P187" s="19" t="n">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="Q187" s="19" t="n">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="R187" s="19" t="n">
         <v>0</v>
@@ -13938,17 +13938,17 @@
       </c>
       <c r="D188" s="14" t="inlineStr">
         <is>
-          <t>1300100085</t>
+          <t>1300100009</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr">
         <is>
-          <t>SFG1010090</t>
+          <t>SFG1010009</t>
         </is>
       </c>
       <c r="F188" s="15" t="inlineStr">
         <is>
-          <t>Painting Top Cover-5603 (232mm) - Ivory</t>
+          <t>Painting Top Cover-5602 (217mm) - Ivory</t>
         </is>
       </c>
       <c r="G188" s="14" t="inlineStr">
@@ -13957,34 +13957,34 @@
         </is>
       </c>
       <c r="H188" s="16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I188" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J188" s="16" t="n">
-        <v>796</v>
+        <v>5587</v>
       </c>
       <c r="K188" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L188" s="16" t="n">
-        <v>796</v>
+        <v>5600</v>
       </c>
       <c r="M188" s="16" t="n">
-        <v>651</v>
+        <v>5290</v>
       </c>
       <c r="N188" s="16" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="O188" s="16" t="n">
-        <v>793</v>
+        <v>5333</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>3</v>
+        <v>267</v>
       </c>
       <c r="Q188" s="16" t="n">
-        <v>3</v>
+        <v>267</v>
       </c>
       <c r="R188" s="16" t="n">
         <v>0</v>
@@ -14004,100 +14004,171 @@
       </c>
       <c r="C189" s="18" t="inlineStr">
         <is>
+          <t>FAN SFG</t>
+        </is>
+      </c>
+      <c r="D189" s="17" t="inlineStr">
+        <is>
+          <t>1300100085</t>
+        </is>
+      </c>
+      <c r="E189" s="18" t="inlineStr">
+        <is>
+          <t>SFG1010090</t>
+        </is>
+      </c>
+      <c r="F189" s="18" t="inlineStr">
+        <is>
+          <t>Painting Top Cover-5603 (232mm) - Ivory</t>
+        </is>
+      </c>
+      <c r="G189" s="17" t="inlineStr">
+        <is>
+          <t>Pcs</t>
+        </is>
+      </c>
+      <c r="H189" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" s="19" t="n">
+        <v>796</v>
+      </c>
+      <c r="K189" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" s="19" t="n">
+        <v>796</v>
+      </c>
+      <c r="M189" s="19" t="n">
+        <v>651</v>
+      </c>
+      <c r="N189" s="19" t="n">
+        <v>142</v>
+      </c>
+      <c r="O189" s="19" t="n">
+        <v>793</v>
+      </c>
+      <c r="P189" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q189" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R189" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" s="18" t="inlineStr"/>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="14" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B190" s="14" t="inlineStr">
+        <is>
+          <t>FAN</t>
+        </is>
+      </c>
+      <c r="C190" s="15" t="inlineStr">
+        <is>
           <t>Printing Process</t>
         </is>
       </c>
-      <c r="D189" s="17" t="inlineStr">
+      <c r="D190" s="14" t="inlineStr">
         <is>
           <t>1800100035</t>
         </is>
       </c>
-      <c r="E189" s="18" t="inlineStr">
+      <c r="E190" s="15" t="inlineStr">
         <is>
           <t>312024211310243</t>
         </is>
       </c>
-      <c r="F189" s="18" t="inlineStr">
+      <c r="F190" s="15" t="inlineStr">
         <is>
           <t>Barcode Printer</t>
         </is>
       </c>
-      <c r="G189" s="17" t="inlineStr">
+      <c r="G190" s="14" t="inlineStr">
         <is>
           <t>Pcs</t>
         </is>
       </c>
-      <c r="H189" s="19" t="n">
+      <c r="H190" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I189" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L189" s="19" t="n">
+      <c r="I190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="M189" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N189" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O189" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P189" s="19" t="n">
+      <c r="M190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="Q189" s="19" t="n">
+      <c r="Q190" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="R189" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" s="18" t="inlineStr"/>
-    </row>
-    <row r="190" ht="24" customHeight="1">
-      <c r="A190" s="20" t="inlineStr">
+      <c r="R190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" s="15" t="inlineStr"/>
+    </row>
+    <row r="191" ht="24" customHeight="1">
+      <c r="A191" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B190" s="20" t="n"/>
-      <c r="C190" s="20" t="n"/>
-      <c r="D190" s="20" t="n"/>
-      <c r="E190" s="20" t="n"/>
-      <c r="F190" s="20" t="inlineStr">
-        <is>
-          <t>186 Items</t>
-        </is>
-      </c>
-      <c r="G190" s="20" t="n"/>
-      <c r="H190" s="21" t="n">
+      <c r="B191" s="20" t="n"/>
+      <c r="C191" s="20" t="n"/>
+      <c r="D191" s="20" t="n"/>
+      <c r="E191" s="20" t="n"/>
+      <c r="F191" s="20" t="inlineStr">
+        <is>
+          <t>187 Items</t>
+        </is>
+      </c>
+      <c r="G191" s="20" t="n"/>
+      <c r="H191" s="21" t="n">
         <v>1053587.01318</v>
       </c>
-      <c r="I190" s="20" t="n"/>
-      <c r="J190" s="20" t="n"/>
-      <c r="K190" s="20" t="n"/>
-      <c r="L190" s="21" t="n">
-        <v>2542768.42028</v>
-      </c>
-      <c r="M190" s="20" t="n"/>
-      <c r="N190" s="20" t="n"/>
-      <c r="O190" s="21" t="n">
-        <v>1330869.88668</v>
-      </c>
-      <c r="P190" s="21" t="n">
-        <v>1211898.5336</v>
-      </c>
-      <c r="Q190" s="20" t="n"/>
-      <c r="R190" s="20" t="n"/>
-      <c r="S190" s="20" t="n"/>
+      <c r="I191" s="20" t="n"/>
+      <c r="J191" s="20" t="n"/>
+      <c r="K191" s="20" t="n"/>
+      <c r="L191" s="21" t="n">
+        <v>2590938.42028</v>
+      </c>
+      <c r="M191" s="20" t="n"/>
+      <c r="N191" s="20" t="n"/>
+      <c r="O191" s="21" t="n">
+        <v>1391737.84068</v>
+      </c>
+      <c r="P191" s="21" t="n">
+        <v>1199200.5796</v>
+      </c>
+      <c r="Q191" s="20" t="n"/>
+      <c r="R191" s="20" t="n"/>
+      <c r="S191" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
